--- a/output/laminas_comunales/comunal_p_aps_a_2018_los_lagos.xlsx
+++ b/output/laminas_comunales/comunal_p_aps_a_2018_los_lagos.xlsx
@@ -352,7 +352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C31"/>
+  <dimension ref="A1:C631"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -375,331 +375,331 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>10303</t>
+          <t>10402</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Purranque</t>
+          <t>Futaleufú</t>
         </is>
       </c>
       <c r="C2">
-        <v>48.4136657714844</v>
+        <v>106330.0234375</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>10107</t>
+          <t>10306</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Llanquihue</t>
+          <t>San Juan de la Costa</t>
         </is>
       </c>
       <c r="C3">
-        <v>48.3642807006836</v>
+        <v>105075.3515625</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>10105</t>
+          <t>10401</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Frutillar</t>
+          <t>Chaitén</t>
         </is>
       </c>
       <c r="C4">
-        <v>47.3229713439941</v>
+        <v>103200.9609375</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10202</t>
+          <t>10403</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Ancud</t>
+          <t>Hualaihué</t>
         </is>
       </c>
       <c r="C5">
-        <v>46.8830490112305</v>
+        <v>100431.453125</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>10203</t>
+          <t>10306</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Chonchi</t>
+          <t>San Juan de la Costa</t>
         </is>
       </c>
       <c r="C6">
-        <v>45.6043968200684</v>
+        <v>100255.140625</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>10404</t>
+          <t>10401</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Palena</t>
+          <t>Chaitén</t>
         </is>
       </c>
       <c r="C7">
-        <v>44.0129432678223</v>
+        <v>100141.6171875</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>10208</t>
+          <t>10103</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Quellón</t>
+          <t>Cochamó</t>
         </is>
       </c>
       <c r="C8">
-        <v>43.6982536315918</v>
+        <v>98950.5390625</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>10201</t>
+          <t>10103</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Castro</t>
+          <t>Cochamó</t>
         </is>
       </c>
       <c r="C9">
-        <v>42.917064666748</v>
+        <v>98453.8359375</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>10305</t>
+          <t>10403</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Río Negro</t>
+          <t>Hualaihué</t>
         </is>
       </c>
       <c r="C10">
-        <v>41.7985000610351</v>
+        <v>97324.6328125</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>10301</t>
+          <t>10102</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Osorno</t>
+          <t>Calbuco</t>
         </is>
       </c>
       <c r="C11">
-        <v>41.5605316162109</v>
+        <v>97036.9609375</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>10204</t>
+          <t>10306</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Curaco de Vélez</t>
+          <t>San Juan de la Costa</t>
         </is>
       </c>
       <c r="C12">
-        <v>40.7407417297363</v>
+        <v>96989.546875</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>10304</t>
+          <t>10208</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Puyehue</t>
+          <t>Quellón</t>
         </is>
       </c>
       <c r="C13">
-        <v>40.2383651733398</v>
+        <v>96119.359375</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>10101</t>
+          <t>10207</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>Queilén</t>
         </is>
       </c>
       <c r="C14">
-        <v>40.1385688781738</v>
+        <v>95835.09375</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>10302</t>
+          <t>10207</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Puerto Octay</t>
+          <t>Queilén</t>
         </is>
       </c>
       <c r="C15">
-        <v>39.6566505432129</v>
+        <v>95513.25</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>10307</t>
+          <t>10207</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>San Pablo</t>
+          <t>Queilén</t>
         </is>
       </c>
       <c r="C16">
-        <v>39.4992332458496</v>
+        <v>95214.5703125</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>10207</t>
+          <t>10209</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Queilén</t>
+          <t>Quemchi</t>
         </is>
       </c>
       <c r="C17">
-        <v>39.4308929443359</v>
+        <v>95058.578125</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>10109</t>
+          <t>10108</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Puerto Varas</t>
+          <t>Maullín</t>
         </is>
       </c>
       <c r="C18">
-        <v>37.5714302062988</v>
+        <v>94830.484375</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>10104</t>
+          <t>10402</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Fresia</t>
+          <t>Futaleufú</t>
         </is>
       </c>
       <c r="C19">
-        <v>36.1169090270996</v>
+        <v>94540.9140625</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>10205</t>
+          <t>10403</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Dalcahue</t>
+          <t>Hualaihué</t>
         </is>
       </c>
       <c r="C20">
-        <v>35.9263648986816</v>
+        <v>94443.3125</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>10403</t>
+          <t>10402</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Hualaihué</t>
+          <t>Futaleufú</t>
         </is>
       </c>
       <c r="C21">
-        <v>35.2828369140625</v>
+        <v>94384.7421875</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>10402</t>
+          <t>10206</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Futaleufú</t>
+          <t>Puqueldón</t>
         </is>
       </c>
       <c r="C22">
-        <v>34.8189430236816</v>
+        <v>94002.1484375</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>10106</t>
+          <t>10306</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Los Muermos</t>
+          <t>San Juan de la Costa</t>
         </is>
       </c>
       <c r="C23">
-        <v>33.8376388549805</v>
+        <v>93775.7421875</v>
       </c>
     </row>
     <row r="24">
@@ -714,112 +714,9112 @@
         </is>
       </c>
       <c r="C24">
-        <v>33.7477798461914</v>
+        <v>93402.03125</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>10102</t>
+          <t>10103</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Calbuco</t>
+          <t>Cochamó</t>
         </is>
       </c>
       <c r="C25">
-        <v>32.8174018859863</v>
+        <v>93398.1015625</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>10206</t>
+          <t>10402</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Puqueldón</t>
+          <t>Futaleufú</t>
         </is>
       </c>
       <c r="C26">
-        <v>32.0175437927246</v>
+        <v>93357.640625</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>10103</t>
+          <t>10210</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Cochamó</t>
+          <t>Quinchao</t>
         </is>
       </c>
       <c r="C27">
-        <v>31.8318309783936</v>
+        <v>93315.890625</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>10108</t>
+          <t>10102</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Maullín</t>
+          <t>Calbuco</t>
         </is>
       </c>
       <c r="C28">
-        <v>29.474515914917</v>
+        <v>93162.625</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>10209</t>
+          <t>10206</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Quemchi</t>
+          <t>Puqueldón</t>
         </is>
       </c>
       <c r="C29">
-        <v>29.4336814880371</v>
+        <v>93139.796875</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>10210</t>
+          <t>10102</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Quinchao</t>
+          <t>Calbuco</t>
         </is>
       </c>
       <c r="C30">
-        <v>28.105094909668</v>
+        <v>93078.1328125</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
+          <t>10404</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Palena</t>
+        </is>
+      </c>
+      <c r="C31">
+        <v>92925.9296875</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>10205</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Dalcahue</t>
+        </is>
+      </c>
+      <c r="C32">
+        <v>92793.8984375</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>10106</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Los Muermos</t>
+        </is>
+      </c>
+      <c r="C33">
+        <v>92603.109375</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>10209</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Quemchi</t>
+        </is>
+      </c>
+      <c r="C34">
+        <v>92491.078125</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>10204</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Curaco de Vélez</t>
+        </is>
+      </c>
+      <c r="C35">
+        <v>92419.6953125</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>10403</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Hualaihué</t>
+        </is>
+      </c>
+      <c r="C36">
+        <v>92263.4296875</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>10404</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Palena</t>
+        </is>
+      </c>
+      <c r="C37">
+        <v>92162.1953125</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>10103</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Cochamó</t>
+        </is>
+      </c>
+      <c r="C38">
+        <v>91865.7734375</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>10401</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Chaitén</t>
+        </is>
+      </c>
+      <c r="C39">
+        <v>91299.140625</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>10209</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Quemchi</t>
+        </is>
+      </c>
+      <c r="C40">
+        <v>90921.0078125</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>10208</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Quellón</t>
+        </is>
+      </c>
+      <c r="C41">
+        <v>90215.8515625</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>10103</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Cochamó</t>
+        </is>
+      </c>
+      <c r="C42">
+        <v>90176.4765625</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>10104</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Fresia</t>
+        </is>
+      </c>
+      <c r="C43">
+        <v>89906.9140625</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>10108</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Maullín</t>
+        </is>
+      </c>
+      <c r="C44">
+        <v>89777.6484375</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>10205</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Dalcahue</t>
+        </is>
+      </c>
+      <c r="C45">
+        <v>89702.8359375</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>10203</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Chonchi</t>
+        </is>
+      </c>
+      <c r="C46">
+        <v>89687.0546875</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>10208</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Quellón</t>
+        </is>
+      </c>
+      <c r="C47">
+        <v>89667.5703125</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>10207</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Queilén</t>
+        </is>
+      </c>
+      <c r="C48">
+        <v>89317.1640625</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>10206</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Puqueldón</t>
+        </is>
+      </c>
+      <c r="C49">
+        <v>89008.5078125</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>10402</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Futaleufú</t>
+        </is>
+      </c>
+      <c r="C50">
+        <v>88783.2265625</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>10207</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Queilén</t>
+        </is>
+      </c>
+      <c r="C51">
+        <v>88752.8203125</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>10101</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Puerto Montt</t>
+        </is>
+      </c>
+      <c r="C52">
+        <v>88510.2734375</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>10401</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Chaitén</t>
+        </is>
+      </c>
+      <c r="C53">
+        <v>88371.4140625</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>10204</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Curaco de Vélez</t>
+        </is>
+      </c>
+      <c r="C54">
+        <v>88244.828125</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>10303</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Purranque</t>
+        </is>
+      </c>
+      <c r="C55">
+        <v>88025.5625</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>10108</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Maullín</t>
+        </is>
+      </c>
+      <c r="C56">
+        <v>87912.78125</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>10205</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Dalcahue</t>
+        </is>
+      </c>
+      <c r="C57">
+        <v>87758.515625</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>10307</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>San Pablo</t>
+        </is>
+      </c>
+      <c r="C58">
+        <v>87619.8984375</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>10202</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Ancud</t>
+        </is>
+      </c>
+      <c r="C59">
+        <v>87209.0703125</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>10404</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Palena</t>
+        </is>
+      </c>
+      <c r="C60">
+        <v>86999.875</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>10102</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Calbuco</t>
+        </is>
+      </c>
+      <c r="C61">
+        <v>86826.515625</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>10208</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Quellón</t>
+        </is>
+      </c>
+      <c r="C62">
+        <v>86722.7109375</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>10403</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Hualaihué</t>
+        </is>
+      </c>
+      <c r="C63">
+        <v>86633.2578125</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>10302</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Puerto Octay</t>
+        </is>
+      </c>
+      <c r="C64">
+        <v>86060.7265625</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>10301</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Osorno</t>
+        </is>
+      </c>
+      <c r="C65">
+        <v>85887.3125</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>10106</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Los Muermos</t>
+        </is>
+      </c>
+      <c r="C66">
+        <v>85833.65625</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>10210</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Quinchao</t>
+        </is>
+      </c>
+      <c r="C67">
+        <v>85438.3671875</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>10208</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Quellón</t>
+        </is>
+      </c>
+      <c r="C68">
+        <v>85364.4765625</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>10105</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Frutillar</t>
+        </is>
+      </c>
+      <c r="C69">
+        <v>85298.1328125</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>10201</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Castro</t>
+        </is>
+      </c>
+      <c r="C70">
+        <v>85150.296875</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>10104</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Fresia</t>
+        </is>
+      </c>
+      <c r="C71">
+        <v>85125.40625</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>10401</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Chaitén</t>
+        </is>
+      </c>
+      <c r="C72">
+        <v>85088.890625</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
           <t>10306</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B73" t="inlineStr">
         <is>
           <t>San Juan de la Costa</t>
         </is>
       </c>
-      <c r="C31">
+      <c r="C73">
+        <v>85062.359375</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>10109</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Puerto Varas</t>
+        </is>
+      </c>
+      <c r="C74">
+        <v>84869.9921875</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>10204</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Curaco de Vélez</t>
+        </is>
+      </c>
+      <c r="C75">
+        <v>84822.1875</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>10403</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Hualaihué</t>
+        </is>
+      </c>
+      <c r="C76">
+        <v>84749.734375</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>10305</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Río Negro</t>
+        </is>
+      </c>
+      <c r="C77">
+        <v>84674.7890625</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>10210</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Quinchao</t>
+        </is>
+      </c>
+      <c r="C78">
+        <v>84655.890625</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>10203</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Chonchi</t>
+        </is>
+      </c>
+      <c r="C79">
+        <v>84580.5390625</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>10209</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Quemchi</t>
+        </is>
+      </c>
+      <c r="C80">
+        <v>84400.7265625</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>10206</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Puqueldón</t>
+        </is>
+      </c>
+      <c r="C81">
+        <v>84218.7421875</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>10106</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Los Muermos</t>
+        </is>
+      </c>
+      <c r="C82">
+        <v>84157.7421875</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>10304</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Puyehue</t>
+        </is>
+      </c>
+      <c r="C83">
+        <v>83919.78125</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>10206</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Puqueldón</t>
+        </is>
+      </c>
+      <c r="C84">
+        <v>83811.1484375</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>10205</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Dalcahue</t>
+        </is>
+      </c>
+      <c r="C85">
+        <v>83683.3984375</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>10104</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Fresia</t>
+        </is>
+      </c>
+      <c r="C86">
+        <v>83532.1640625</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>10401</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Chaitén</t>
+        </is>
+      </c>
+      <c r="C87">
+        <v>83360.984375</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>10208</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Quellón</t>
+        </is>
+      </c>
+      <c r="C88">
+        <v>83166.734375</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>10108</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Maullín</t>
+        </is>
+      </c>
+      <c r="C89">
+        <v>83161.3828125</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>10306</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>San Juan de la Costa</t>
+        </is>
+      </c>
+      <c r="C90">
+        <v>82927.875</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>10402</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Futaleufú</t>
+        </is>
+      </c>
+      <c r="C91">
+        <v>82859.7890625</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>10103</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Cochamó</t>
+        </is>
+      </c>
+      <c r="C92">
+        <v>81752.8984375</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>10203</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Chonchi</t>
+        </is>
+      </c>
+      <c r="C93">
+        <v>81500.84375</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>10106</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Los Muermos</t>
+        </is>
+      </c>
+      <c r="C94">
+        <v>81337.5546875</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>10207</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Queilén</t>
+        </is>
+      </c>
+      <c r="C95">
+        <v>80958.3671875</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>10404</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Palena</t>
+        </is>
+      </c>
+      <c r="C96">
+        <v>80835.671875</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>10102</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Calbuco</t>
+        </is>
+      </c>
+      <c r="C97">
+        <v>80414.53125</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>10202</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Ancud</t>
+        </is>
+      </c>
+      <c r="C98">
+        <v>80268.75</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>10204</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Curaco de Vélez</t>
+        </is>
+      </c>
+      <c r="C99">
+        <v>80187.15625</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>10101</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Puerto Montt</t>
+        </is>
+      </c>
+      <c r="C100">
+        <v>80178.7109375</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>10102</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Calbuco</t>
+        </is>
+      </c>
+      <c r="C101">
+        <v>80130.5390625</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>10107</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Llanquihue</t>
+        </is>
+      </c>
+      <c r="C102">
+        <v>80069.8828125</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>10205</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Dalcahue</t>
+        </is>
+      </c>
+      <c r="C103">
+        <v>79221.328125</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>10202</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Ancud</t>
+        </is>
+      </c>
+      <c r="C104">
+        <v>79134.6796875</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>10201</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Castro</t>
+        </is>
+      </c>
+      <c r="C105">
+        <v>78830.53125</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>10210</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Quinchao</t>
+        </is>
+      </c>
+      <c r="C106">
+        <v>78820.1484375</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>10101</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Puerto Montt</t>
+        </is>
+      </c>
+      <c r="C107">
+        <v>78775.6015625</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>10204</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Curaco de Vélez</t>
+        </is>
+      </c>
+      <c r="C108">
+        <v>78534.9609375</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>10305</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Río Negro</t>
+        </is>
+      </c>
+      <c r="C109">
+        <v>78410.1953125</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>10104</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Fresia</t>
+        </is>
+      </c>
+      <c r="C110">
+        <v>78307.0625</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>10307</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>San Pablo</t>
+        </is>
+      </c>
+      <c r="C111">
+        <v>78207.484375</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>10302</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Puerto Octay</t>
+        </is>
+      </c>
+      <c r="C112">
+        <v>78165.859375</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>10307</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>San Pablo</t>
+        </is>
+      </c>
+      <c r="C113">
+        <v>78031.328125</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>10304</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Puyehue</t>
+        </is>
+      </c>
+      <c r="C114">
+        <v>77992.40625</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>10104</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Fresia</t>
+        </is>
+      </c>
+      <c r="C115">
+        <v>77808.84375</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>10106</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Los Muermos</t>
+        </is>
+      </c>
+      <c r="C116">
+        <v>77765.34375</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>10203</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Chonchi</t>
+        </is>
+      </c>
+      <c r="C117">
+        <v>77655.4453125</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>10109</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Puerto Varas</t>
+        </is>
+      </c>
+      <c r="C118">
+        <v>77616.46875</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>10108</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Maullín</t>
+        </is>
+      </c>
+      <c r="C119">
+        <v>77588.515625</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>10304</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Puyehue</t>
+        </is>
+      </c>
+      <c r="C120">
+        <v>77377.140625</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>10101</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Puerto Montt</t>
+        </is>
+      </c>
+      <c r="C121">
+        <v>76811.4453125</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>10205</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Dalcahue</t>
+        </is>
+      </c>
+      <c r="C122">
+        <v>76727.453125</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>10105</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Frutillar</t>
+        </is>
+      </c>
+      <c r="C123">
+        <v>76438.875</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>10209</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Quemchi</t>
+        </is>
+      </c>
+      <c r="C124">
+        <v>76404.4921875</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>10103</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Cochamó</t>
+        </is>
+      </c>
+      <c r="C125">
+        <v>76392.8359375</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>10209</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Quemchi</t>
+        </is>
+      </c>
+      <c r="C126">
+        <v>76222.7421875</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>10303</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Purranque</t>
+        </is>
+      </c>
+      <c r="C127">
+        <v>76016.0078125</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>10109</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Puerto Varas</t>
+        </is>
+      </c>
+      <c r="C128">
+        <v>75796.9375</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>10107</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Llanquihue</t>
+        </is>
+      </c>
+      <c r="C129">
+        <v>75702.25</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>10307</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>San Pablo</t>
+        </is>
+      </c>
+      <c r="C130">
+        <v>75550.359375</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>10202</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Ancud</t>
+        </is>
+      </c>
+      <c r="C131">
+        <v>75531.265625</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>10108</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Maullín</t>
+        </is>
+      </c>
+      <c r="C132">
+        <v>75422.8515625</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>10106</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Los Muermos</t>
+        </is>
+      </c>
+      <c r="C133">
+        <v>75362.765625</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>10101</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Puerto Montt</t>
+        </is>
+      </c>
+      <c r="C134">
+        <v>75298.2421875</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>10109</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Puerto Varas</t>
+        </is>
+      </c>
+      <c r="C135">
+        <v>75257.671875</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>10203</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Chonchi</t>
+        </is>
+      </c>
+      <c r="C136">
+        <v>75256.4765625</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>10302</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Puerto Octay</t>
+        </is>
+      </c>
+      <c r="C137">
+        <v>74870.140625</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>10201</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Castro</t>
+        </is>
+      </c>
+      <c r="C138">
+        <v>74831.3046875</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>10109</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Puerto Varas</t>
+        </is>
+      </c>
+      <c r="C139">
+        <v>74761.3671875</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>10105</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Frutillar</t>
+        </is>
+      </c>
+      <c r="C140">
+        <v>74518.7734375</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>10304</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Puyehue</t>
+        </is>
+      </c>
+      <c r="C141">
+        <v>74450.984375</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>10302</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Puerto Octay</t>
+        </is>
+      </c>
+      <c r="C142">
+        <v>74414.890625</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>10301</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Osorno</t>
+        </is>
+      </c>
+      <c r="C143">
+        <v>74310.375</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>10302</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Puerto Octay</t>
+        </is>
+      </c>
+      <c r="C144">
+        <v>73956.25</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>10107</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Llanquihue</t>
+        </is>
+      </c>
+      <c r="C145">
+        <v>73762.921875</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>10303</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Purranque</t>
+        </is>
+      </c>
+      <c r="C146">
+        <v>73678.84375</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>10305</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Río Negro</t>
+        </is>
+      </c>
+      <c r="C147">
+        <v>73662.203125</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>10305</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Río Negro</t>
+        </is>
+      </c>
+      <c r="C148">
+        <v>73599.65625</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>10305</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Río Negro</t>
+        </is>
+      </c>
+      <c r="C149">
+        <v>73536.3828125</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>10202</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Ancud</t>
+        </is>
+      </c>
+      <c r="C150">
+        <v>73454.3515625</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>10303</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Purranque</t>
+        </is>
+      </c>
+      <c r="C151">
+        <v>73334.578125</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>10303</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Purranque</t>
+        </is>
+      </c>
+      <c r="C152">
+        <v>73011.9296875</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>10403</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Hualaihué</t>
+        </is>
+      </c>
+      <c r="C153">
+        <v>72978.9375</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>10210</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Quinchao</t>
+        </is>
+      </c>
+      <c r="C154">
+        <v>72975.7265625</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>10304</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Puyehue</t>
+        </is>
+      </c>
+      <c r="C155">
+        <v>72960.9140625</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>10105</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Frutillar</t>
+        </is>
+      </c>
+      <c r="C156">
+        <v>72913.421875</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>10204</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Curaco de Vélez</t>
+        </is>
+      </c>
+      <c r="C157">
+        <v>72414.8203125</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>10107</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Llanquihue</t>
+        </is>
+      </c>
+      <c r="C158">
+        <v>72312.1171875</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>10202</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Ancud</t>
+        </is>
+      </c>
+      <c r="C159">
+        <v>72252.359375</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>10307</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>San Pablo</t>
+        </is>
+      </c>
+      <c r="C160">
+        <v>72161.625</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>10201</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Castro</t>
+        </is>
+      </c>
+      <c r="C161">
+        <v>72102.6171875</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>10104</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Fresia</t>
+        </is>
+      </c>
+      <c r="C162">
+        <v>72021.3203125</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>10203</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Chonchi</t>
+        </is>
+      </c>
+      <c r="C163">
+        <v>71969.15625</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>10304</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Puyehue</t>
+        </is>
+      </c>
+      <c r="C164">
+        <v>71720.9375</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>10307</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>San Pablo</t>
+        </is>
+      </c>
+      <c r="C165">
+        <v>71449.8203125</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>10301</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Osorno</t>
+        </is>
+      </c>
+      <c r="C166">
+        <v>71295.109375</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>10301</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Osorno</t>
+        </is>
+      </c>
+      <c r="C167">
+        <v>71201.25</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>10206</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Puqueldón</t>
+        </is>
+      </c>
+      <c r="C168">
+        <v>71173.53125</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>10306</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>San Juan de la Costa</t>
+        </is>
+      </c>
+      <c r="C169">
+        <v>71147.4453125</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>10301</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Osorno</t>
+        </is>
+      </c>
+      <c r="C170">
+        <v>71058.734375</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>10101</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Puerto Montt</t>
+        </is>
+      </c>
+      <c r="C171">
+        <v>71025.3828125</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>10107</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Llanquihue</t>
+        </is>
+      </c>
+      <c r="C172">
+        <v>70959.3046875</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>10302</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Puerto Octay</t>
+        </is>
+      </c>
+      <c r="C173">
+        <v>69701.5078125</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>10105</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Frutillar</t>
+        </is>
+      </c>
+      <c r="C174">
+        <v>69689.3828125</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>10109</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Puerto Varas</t>
+        </is>
+      </c>
+      <c r="C175">
+        <v>69678.171875</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>10404</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Palena</t>
+        </is>
+      </c>
+      <c r="C176">
+        <v>69332.171875</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>10404</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Palena</t>
+        </is>
+      </c>
+      <c r="C177">
+        <v>68969.359375</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>10107</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Llanquihue</t>
+        </is>
+      </c>
+      <c r="C178">
+        <v>68532.53125</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>10303</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Purranque</t>
+        </is>
+      </c>
+      <c r="C179">
+        <v>68262.0390625</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>10305</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Río Negro</t>
+        </is>
+      </c>
+      <c r="C180">
+        <v>68237.8515625</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>10201</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>Castro</t>
+        </is>
+      </c>
+      <c r="C181">
+        <v>67927.40625</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>10201</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Castro</t>
+        </is>
+      </c>
+      <c r="C182">
+        <v>67479.3828125</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>10210</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Quinchao</t>
+        </is>
+      </c>
+      <c r="C183">
+        <v>66330.609375</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>10105</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>Frutillar</t>
+        </is>
+      </c>
+      <c r="C184">
+        <v>65499.4609375</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>10102</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>Calbuco</t>
+        </is>
+      </c>
+      <c r="C185">
+        <v>65199.25390625</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>10301</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>Osorno</t>
+        </is>
+      </c>
+      <c r="C186">
+        <v>65158.02734375</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>10402</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>Futaleufú</t>
+        </is>
+      </c>
+      <c r="C187">
+        <v>64177.9375</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>10206</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>Puqueldón</t>
+        </is>
+      </c>
+      <c r="C188">
+        <v>63528.44921875</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>10109</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Puerto Varas</t>
+        </is>
+      </c>
+      <c r="C189">
+        <v>63442.6328125</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>10207</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>Queilén</t>
+        </is>
+      </c>
+      <c r="C190">
+        <v>63408.02734375</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>10404</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>Palena</t>
+        </is>
+      </c>
+      <c r="C191">
+        <v>62728.05078125</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>10205</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>Dalcahue</t>
+        </is>
+      </c>
+      <c r="C192">
+        <v>62123.62890625</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>10208</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>Quellón</t>
+        </is>
+      </c>
+      <c r="C193">
+        <v>61661.01171875</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>10105</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>Frutillar</t>
+        </is>
+      </c>
+      <c r="C194">
+        <v>61167.66015625</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>10106</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>Los Muermos</t>
+        </is>
+      </c>
+      <c r="C195">
+        <v>60959.12890625</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>10107</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>Llanquihue</t>
+        </is>
+      </c>
+      <c r="C196">
+        <v>60453.484375</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>10108</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>Maullín</t>
+        </is>
+      </c>
+      <c r="C197">
+        <v>60303.99609375</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>10101</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Puerto Montt</t>
+        </is>
+      </c>
+      <c r="C198">
+        <v>58930.9375</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>10302</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>Puerto Octay</t>
+        </is>
+      </c>
+      <c r="C199">
+        <v>58839.15625</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>10203</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Chonchi</t>
+        </is>
+      </c>
+      <c r="C200">
+        <v>58808.109375</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>10210</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Quinchao</t>
+        </is>
+      </c>
+      <c r="C201">
+        <v>58094.71484375</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>10104</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>Fresia</t>
+        </is>
+      </c>
+      <c r="C202">
+        <v>58041.6484375</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>10202</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>Ancud</t>
+        </is>
+      </c>
+      <c r="C203">
+        <v>57904.49609375</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>10204</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>Curaco de Vélez</t>
+        </is>
+      </c>
+      <c r="C204">
+        <v>57566.12109375</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>10304</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>Puyehue</t>
+        </is>
+      </c>
+      <c r="C205">
+        <v>57553.796875</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>10303</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>Purranque</t>
+        </is>
+      </c>
+      <c r="C206">
+        <v>57506.30078125</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>10305</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>Río Negro</t>
+        </is>
+      </c>
+      <c r="C207">
+        <v>57177.80859375</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>10307</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>San Pablo</t>
+        </is>
+      </c>
+      <c r="C208">
+        <v>56528.55859375</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>10301</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>Osorno</t>
+        </is>
+      </c>
+      <c r="C209">
+        <v>56417.390625</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>10201</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>Castro</t>
+        </is>
+      </c>
+      <c r="C210">
+        <v>56375.53515625</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>10209</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>Quemchi</t>
+        </is>
+      </c>
+      <c r="C211">
+        <v>55552.74609375</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>10306</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>San Juan de la Costa</t>
+        </is>
+      </c>
+      <c r="C212">
+        <v>78.0361785888672</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>10103</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>Cochamó</t>
+        </is>
+      </c>
+      <c r="C213">
+        <v>77.6595764160156</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>10209</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>Quemchi</t>
+        </is>
+      </c>
+      <c r="C214">
+        <v>75.0649337768555</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>10206</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>Puqueldón</t>
+        </is>
+      </c>
+      <c r="C215">
+        <v>71.7703323364258</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>10306</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>San Juan de la Costa</t>
+        </is>
+      </c>
+      <c r="C216">
+        <v>70.10622406005859</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>10209</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>Quemchi</t>
+        </is>
+      </c>
+      <c r="C217">
+        <v>69.7841720581055</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>10206</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>Puqueldón</t>
+        </is>
+      </c>
+      <c r="C218">
+        <v>69.74359130859381</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>10209</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>Quemchi</t>
+        </is>
+      </c>
+      <c r="C219">
+        <v>69.3259963989258</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>10306</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>San Juan de la Costa</t>
+        </is>
+      </c>
+      <c r="C220">
+        <v>68.9781036376953</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>10403</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>Hualaihué</t>
+        </is>
+      </c>
+      <c r="C221">
+        <v>68.6991882324219</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>10103</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>Cochamó</t>
+        </is>
+      </c>
+      <c r="C222">
+        <v>67.3981170654297</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>10401</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>Chaitén</t>
+        </is>
+      </c>
+      <c r="C223">
+        <v>67.2566375732422</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>10206</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>Puqueldón</t>
+        </is>
+      </c>
+      <c r="C224">
+        <v>65.5737686157227</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>10108</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>Maullín</t>
+        </is>
+      </c>
+      <c r="C225">
+        <v>65.4545440673828</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>10210</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>Quinchao</t>
+        </is>
+      </c>
+      <c r="C226">
+        <v>65.3992385864258</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>10204</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>Curaco de Vélez</t>
+        </is>
+      </c>
+      <c r="C227">
+        <v>64.51612854003911</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>10205</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>Dalcahue</t>
+        </is>
+      </c>
+      <c r="C228">
+        <v>64.4490661621094</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>10210</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>Quinchao</t>
+        </is>
+      </c>
+      <c r="C229">
+        <v>64.3312072753906</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>10108</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>Maullín</t>
+        </is>
+      </c>
+      <c r="C230">
+        <v>64.1878662109375</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>10102</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>Calbuco</t>
+        </is>
+      </c>
+      <c r="C231">
+        <v>64.143424987793</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>10103</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>Cochamó</t>
+        </is>
+      </c>
+      <c r="C232">
+        <v>64.0350875854492</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>10205</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>Dalcahue</t>
+        </is>
+      </c>
+      <c r="C233">
+        <v>63.5782737731934</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>10210</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>Quinchao</t>
+        </is>
+      </c>
+      <c r="C234">
+        <v>63.191764831543</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>10306</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>San Juan de la Costa</t>
+        </is>
+      </c>
+      <c r="C235">
+        <v>62.6547470092773</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>10108</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>Maullín</t>
+        </is>
+      </c>
+      <c r="C236">
+        <v>62.5806465148926</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>10207</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>Queilén</t>
+        </is>
+      </c>
+      <c r="C237">
+        <v>62.4161071777344</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>10207</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>Queilén</t>
+        </is>
+      </c>
+      <c r="C238">
+        <v>62.0320854187012</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>10209</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>Quemchi</t>
+        </is>
+      </c>
+      <c r="C239">
+        <v>61.624439239502</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>10207</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>Queilén</t>
+        </is>
+      </c>
+      <c r="C240">
+        <v>60.8478813171387</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>10403</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>Hualaihué</t>
+        </is>
+      </c>
+      <c r="C241">
+        <v>59.5854911804199</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>10102</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>Calbuco</t>
+        </is>
+      </c>
+      <c r="C242">
+        <v>59.4444427490234</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>10205</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>Dalcahue</t>
+        </is>
+      </c>
+      <c r="C243">
+        <v>59.1534385681152</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>10106</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>Los Muermos</t>
+        </is>
+      </c>
+      <c r="C244">
+        <v>58.9416046142578</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>10206</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>Puqueldón</t>
+        </is>
+      </c>
+      <c r="C245">
+        <v>58.7719306945801</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>10106</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>Los Muermos</t>
+        </is>
+      </c>
+      <c r="C246">
+        <v>58.6443252563477</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>10204</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>Curaco de Vélez</t>
+        </is>
+      </c>
+      <c r="C247">
+        <v>58.2677154541016</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>10103</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>Cochamó</t>
+        </is>
+      </c>
+      <c r="C248">
+        <v>58.2582588195801</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>10108</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>Maullín</t>
+        </is>
+      </c>
+      <c r="C249">
+        <v>57.9217681884766</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>10210</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>Quinchao</t>
+        </is>
+      </c>
+      <c r="C250">
+        <v>57.8821640014649</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>10103</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>Cochamó</t>
+        </is>
+      </c>
+      <c r="C251">
+        <v>57.8616371154785</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>10204</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>Curaco de Vélez</t>
+        </is>
+      </c>
+      <c r="C252">
+        <v>57.5197906494141</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>10403</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>Hualaihué</t>
+        </is>
+      </c>
+      <c r="C253">
+        <v>57.2533836364746</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>10102</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>Calbuco</t>
+        </is>
+      </c>
+      <c r="C254">
+        <v>56.8019104003906</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>10306</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>San Juan de la Costa</t>
+        </is>
+      </c>
+      <c r="C255">
+        <v>56.4779891967773</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>10401</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>Chaitén</t>
+        </is>
+      </c>
+      <c r="C256">
+        <v>56.3025207519531</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>10106</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>Los Muermos</t>
+        </is>
+      </c>
+      <c r="C257">
+        <v>56.2594261169434</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>10402</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>Futaleufú</t>
+        </is>
+      </c>
+      <c r="C258">
+        <v>56.1224479675293</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>10210</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>Quinchao</t>
+        </is>
+      </c>
+      <c r="C259">
+        <v>55.9006195068359</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>10208</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>Quellón</t>
+        </is>
+      </c>
+      <c r="C260">
+        <v>55.8758316040039</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>10306</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>San Juan de la Costa</t>
+        </is>
+      </c>
+      <c r="C261">
+        <v>55.46875</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>10108</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>Maullín</t>
+        </is>
+      </c>
+      <c r="C262">
+        <v>54.9844245910645</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>10404</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>Palena</t>
+        </is>
+      </c>
+      <c r="C263">
+        <v>54.761905670166</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>10209</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>Quemchi</t>
+        </is>
+      </c>
+      <c r="C264">
+        <v>54.5150489807129</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>10107</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>Llanquihue</t>
+        </is>
+      </c>
+      <c r="C265">
+        <v>54.1947937011719</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>10401</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>Chaitén</t>
+        </is>
+      </c>
+      <c r="C266">
+        <v>53.754940032959</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>10402</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>Futaleufú</t>
+        </is>
+      </c>
+      <c r="C267">
+        <v>53.75</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>10108</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>Maullín</t>
+        </is>
+      </c>
+      <c r="C268">
+        <v>53.4469413757324</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>10105</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>Frutillar</t>
+        </is>
+      </c>
+      <c r="C269">
+        <v>52.7390899658203</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>10209</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>Quemchi</t>
+        </is>
+      </c>
+      <c r="C270">
+        <v>52.5203247070312</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>10102</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>Calbuco</t>
+        </is>
+      </c>
+      <c r="C271">
+        <v>52.2066497802734</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>10206</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>Puqueldón</t>
+        </is>
+      </c>
+      <c r="C272">
+        <v>52.1212120056152</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>10107</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>Llanquihue</t>
+        </is>
+      </c>
+      <c r="C273">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>10303</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>Purranque</t>
+        </is>
+      </c>
+      <c r="C274">
+        <v>51.3386878967285</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>10403</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>Hualaihué</t>
+        </is>
+      </c>
+      <c r="C275">
+        <v>51.3108596801758</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>10205</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>Dalcahue</t>
+        </is>
+      </c>
+      <c r="C276">
+        <v>51.2470321655273</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>10207</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>Queilén</t>
+        </is>
+      </c>
+      <c r="C277">
+        <v>51.1415519714355</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>10303</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>Purranque</t>
+        </is>
+      </c>
+      <c r="C278">
+        <v>51.1029396057129</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>10208</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>Quellón</t>
+        </is>
+      </c>
+      <c r="C279">
+        <v>51.0917015075684</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>10105</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>Frutillar</t>
+        </is>
+      </c>
+      <c r="C280">
+        <v>51.0489501953125</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>10404</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>Palena</t>
+        </is>
+      </c>
+      <c r="C281">
+        <v>51.0204086303711</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>10203</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>Chonchi</t>
+        </is>
+      </c>
+      <c r="C282">
+        <v>50.4587173461914</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>10207</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>Queilén</t>
+        </is>
+      </c>
+      <c r="C283">
+        <v>50.2710037231445</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>10106</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>Los Muermos</t>
+        </is>
+      </c>
+      <c r="C284">
+        <v>50.25830078125</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>10403</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>Hualaihué</t>
+        </is>
+      </c>
+      <c r="C285">
+        <v>50.2396926879883</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>10204</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>Curaco de Vélez</t>
+        </is>
+      </c>
+      <c r="C286">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>10204</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>Curaco de Vélez</t>
+        </is>
+      </c>
+      <c r="C287">
+        <v>49.9194831848145</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>10103</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>Cochamó</t>
+        </is>
+      </c>
+      <c r="C288">
+        <v>49.8559074401855</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>10102</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>Calbuco</t>
+        </is>
+      </c>
+      <c r="C289">
+        <v>49.6779403686523</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>10204</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>Curaco de Vélez</t>
+        </is>
+      </c>
+      <c r="C290">
+        <v>49.5867767333984</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>10210</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>Quinchao</t>
+        </is>
+      </c>
+      <c r="C291">
+        <v>49.2693099975586</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>10207</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>Queilén</t>
+        </is>
+      </c>
+      <c r="C292">
+        <v>49.2581596374512</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>10402</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>Futaleufú</t>
+        </is>
+      </c>
+      <c r="C293">
+        <v>48.7437171936035</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>10107</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>Llanquihue</t>
+        </is>
+      </c>
+      <c r="C294">
+        <v>48.7394943237305</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>10307</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>San Pablo</t>
+        </is>
+      </c>
+      <c r="C295">
+        <v>48.6515655517578</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>10404</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>Palena</t>
+        </is>
+      </c>
+      <c r="C296">
+        <v>48.6111106872559</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>10202</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>Ancud</t>
+        </is>
+      </c>
+      <c r="C297">
+        <v>48.5864562988281</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>10202</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>Ancud</t>
+        </is>
+      </c>
+      <c r="C298">
+        <v>48.5607490539551</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>10206</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>Puqueldón</t>
+        </is>
+      </c>
+      <c r="C299">
+        <v>48.5148506164551</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>10303</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>Purranque</t>
+        </is>
+      </c>
+      <c r="C300">
+        <v>48.4136657714844</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>10107</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>Llanquihue</t>
+        </is>
+      </c>
+      <c r="C301">
+        <v>48.3642807006836</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>10105</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>Frutillar</t>
+        </is>
+      </c>
+      <c r="C302">
+        <v>48.2625465393066</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>10208</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>Quellón</t>
+        </is>
+      </c>
+      <c r="C303">
+        <v>48.2142868041992</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>10303</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>Purranque</t>
+        </is>
+      </c>
+      <c r="C304">
+        <v>48.2014389038086</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>10207</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>Queilén</t>
+        </is>
+      </c>
+      <c r="C305">
+        <v>48.0874328613281</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>10204</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>Curaco de Vélez</t>
+        </is>
+      </c>
+      <c r="C306">
+        <v>48.0769233703613</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>10202</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>Ancud</t>
+        </is>
+      </c>
+      <c r="C307">
+        <v>47.8801155090332</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>10108</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>Maullín</t>
+        </is>
+      </c>
+      <c r="C308">
+        <v>47.8654594421387</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>10203</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>Chonchi</t>
+        </is>
+      </c>
+      <c r="C309">
+        <v>47.765007019043</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>10205</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>Dalcahue</t>
+        </is>
+      </c>
+      <c r="C310">
+        <v>47.7218208312988</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>10205</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>Dalcahue</t>
+        </is>
+      </c>
+      <c r="C311">
+        <v>47.357292175293</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>10105</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>Frutillar</t>
+        </is>
+      </c>
+      <c r="C312">
+        <v>47.3229713439941</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>10102</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>Calbuco</t>
+        </is>
+      </c>
+      <c r="C313">
+        <v>47.1107177734375</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>10104</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>Fresia</t>
+        </is>
+      </c>
+      <c r="C314">
+        <v>47.0766143798828</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>10202</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>Ancud</t>
+        </is>
+      </c>
+      <c r="C315">
+        <v>46.8830490112305</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>10306</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>San Juan de la Costa</t>
+        </is>
+      </c>
+      <c r="C316">
+        <v>46.6992683410645</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>10106</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>Los Muermos</t>
+        </is>
+      </c>
+      <c r="C317">
+        <v>46.5892601013184</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>10303</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>Purranque</t>
+        </is>
+      </c>
+      <c r="C318">
+        <v>46.5116271972656</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>10107</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>Llanquihue</t>
+        </is>
+      </c>
+      <c r="C319">
+        <v>46.4223403930664</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>10208</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>Quellón</t>
+        </is>
+      </c>
+      <c r="C320">
+        <v>46.3687133789062</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>10208</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>Quellón</t>
+        </is>
+      </c>
+      <c r="C321">
+        <v>46.330680847168</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>10303</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>Purranque</t>
+        </is>
+      </c>
+      <c r="C322">
+        <v>45.9641265869141</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>10208</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>Quellón</t>
+        </is>
+      </c>
+      <c r="C323">
+        <v>45.9252166748047</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>10402</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>Futaleufú</t>
+        </is>
+      </c>
+      <c r="C324">
+        <v>45.9183654785156</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>10203</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>Chonchi</t>
+        </is>
+      </c>
+      <c r="C325">
+        <v>45.8598709106445</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>10203</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>Chonchi</t>
+        </is>
+      </c>
+      <c r="C326">
+        <v>45.8244094848633</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>10209</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>Quemchi</t>
+        </is>
+      </c>
+      <c r="C327">
+        <v>45.7894744873047</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>10202</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>Ancud</t>
+        </is>
+      </c>
+      <c r="C328">
+        <v>45.6447982788086</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>10203</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>Chonchi</t>
+        </is>
+      </c>
+      <c r="C329">
+        <v>45.6043968200684</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>10206</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>Puqueldón</t>
+        </is>
+      </c>
+      <c r="C330">
+        <v>45.4887199401855</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>10401</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>Chaitén</t>
+        </is>
+      </c>
+      <c r="C331">
+        <v>45.4706916809082</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>10202</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>Ancud</t>
+        </is>
+      </c>
+      <c r="C332">
+        <v>45.4574317932129</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>10203</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>Chonchi</t>
+        </is>
+      </c>
+      <c r="C333">
+        <v>45.4005928039551</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>10403</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>Hualaihué</t>
+        </is>
+      </c>
+      <c r="C334">
+        <v>45.4005928039551</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>10105</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>Frutillar</t>
+        </is>
+      </c>
+      <c r="C335">
+        <v>45.2926216125488</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>10107</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>Llanquihue</t>
+        </is>
+      </c>
+      <c r="C336">
+        <v>45.216251373291</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>10305</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>Río Negro</t>
+        </is>
+      </c>
+      <c r="C337">
+        <v>44.9917907714844</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>10404</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>Palena</t>
+        </is>
+      </c>
+      <c r="C338">
+        <v>44.8979606628418</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>10210</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>Quinchao</t>
+        </is>
+      </c>
+      <c r="C339">
+        <v>44.817928314209</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>10304</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>Puyehue</t>
+        </is>
+      </c>
+      <c r="C340">
+        <v>44.7661476135254</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>10105</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>Frutillar</t>
+        </is>
+      </c>
+      <c r="C341">
+        <v>44.5969123840332</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>10303</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>Purranque</t>
+        </is>
+      </c>
+      <c r="C342">
+        <v>44.2879486083984</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>10203</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>Chonchi</t>
+        </is>
+      </c>
+      <c r="C343">
+        <v>44.1658630371094</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>10404</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>Palena</t>
+        </is>
+      </c>
+      <c r="C344">
+        <v>44.0129432678223</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>10203</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>Chonchi</t>
+        </is>
+      </c>
+      <c r="C345">
+        <v>43.9729995727539</v>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>10207</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>Queilén</t>
+        </is>
+      </c>
+      <c r="C346">
+        <v>43.7158470153809</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>10208</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>Quellón</t>
+        </is>
+      </c>
+      <c r="C347">
+        <v>43.6982536315918</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>10107</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>Llanquihue</t>
+        </is>
+      </c>
+      <c r="C348">
+        <v>43.4285697937012</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>10307</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>San Pablo</t>
+        </is>
+      </c>
+      <c r="C349">
+        <v>43.400447845459</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>10403</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>Hualaihué</t>
+        </is>
+      </c>
+      <c r="C350">
+        <v>43.3460083007812</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>10301</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>Osorno</t>
+        </is>
+      </c>
+      <c r="C351">
+        <v>43.2754249572754</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>10404</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>Palena</t>
+        </is>
+      </c>
+      <c r="C352">
+        <v>43.2098770141602</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>10201</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>Castro</t>
+        </is>
+      </c>
+      <c r="C353">
+        <v>43.1818199157715</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>10201</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>Castro</t>
+        </is>
+      </c>
+      <c r="C354">
+        <v>43.1506843566895</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>10201</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>Castro</t>
+        </is>
+      </c>
+      <c r="C355">
+        <v>42.917064666748</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>10402</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>Futaleufú</t>
+        </is>
+      </c>
+      <c r="C356">
+        <v>42.8969345092773</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>10302</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>Puerto Octay</t>
+        </is>
+      </c>
+      <c r="C357">
+        <v>42.7083320617676</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>10105</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>Frutillar</t>
+        </is>
+      </c>
+      <c r="C358">
+        <v>42.6150131225586</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>10201</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>Castro</t>
+        </is>
+      </c>
+      <c r="C359">
+        <v>42.5404167175293</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>10201</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>Castro</t>
+        </is>
+      </c>
+      <c r="C360">
+        <v>42.5196838378906</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>10304</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>Puyehue</t>
+        </is>
+      </c>
+      <c r="C361">
+        <v>42.4920120239258</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>10106</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>Los Muermos</t>
+        </is>
+      </c>
+      <c r="C362">
+        <v>42.376522064209</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>10201</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>Castro</t>
+        </is>
+      </c>
+      <c r="C363">
+        <v>42.3428916931152</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>10203</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>Chonchi</t>
+        </is>
+      </c>
+      <c r="C364">
+        <v>42.2505302429199</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>10305</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>Río Negro</t>
+        </is>
+      </c>
+      <c r="C365">
+        <v>42.196533203125</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>10202</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>Ancud</t>
+        </is>
+      </c>
+      <c r="C366">
+        <v>42.1955413818359</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>10104</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>Fresia</t>
+        </is>
+      </c>
+      <c r="C367">
+        <v>42.1487617492676</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>10103</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>Cochamó</t>
+        </is>
+      </c>
+      <c r="C368">
+        <v>41.9512176513672</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>10205</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>Dalcahue</t>
+        </is>
+      </c>
+      <c r="C369">
+        <v>41.9485778808594</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>10301</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>Osorno</t>
+        </is>
+      </c>
+      <c r="C370">
+        <v>41.9365386962891</v>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>10307</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>San Pablo</t>
+        </is>
+      </c>
+      <c r="C371">
+        <v>41.8446617126465</v>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>10305</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>Río Negro</t>
+        </is>
+      </c>
+      <c r="C372">
+        <v>41.7985000610351</v>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>10208</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>Quellón</t>
+        </is>
+      </c>
+      <c r="C373">
+        <v>41.6445617675781</v>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>10307</t>
+        </is>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>San Pablo</t>
+        </is>
+      </c>
+      <c r="C374">
+        <v>41.5999984741211</v>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>10301</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>Osorno</t>
+        </is>
+      </c>
+      <c r="C375">
+        <v>41.5605316162109</v>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>10301</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>Osorno</t>
+        </is>
+      </c>
+      <c r="C376">
+        <v>41.5057525634766</v>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>10204</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>Curaco de Vélez</t>
+        </is>
+      </c>
+      <c r="C377">
+        <v>41.4473686218262</v>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>10305</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>Río Negro</t>
+        </is>
+      </c>
+      <c r="C378">
+        <v>41.3937873840332</v>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>10205</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>Dalcahue</t>
+        </is>
+      </c>
+      <c r="C379">
+        <v>41.2470016479492</v>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>10205</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>Dalcahue</t>
+        </is>
+      </c>
+      <c r="C380">
+        <v>41.1366729736328</v>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>10101</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>Puerto Montt</t>
+        </is>
+      </c>
+      <c r="C381">
+        <v>41.024715423584</v>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>10301</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>Osorno</t>
+        </is>
+      </c>
+      <c r="C382">
+        <v>41.0042343139649</v>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>10305</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>Río Negro</t>
+        </is>
+      </c>
+      <c r="C383">
+        <v>41.0022773742676</v>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>10104</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>Fresia</t>
+        </is>
+      </c>
+      <c r="C384">
+        <v>40.8898315429688</v>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>10201</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>Castro</t>
+        </is>
+      </c>
+      <c r="C385">
+        <v>40.8675804138184</v>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>10305</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>Río Negro</t>
+        </is>
+      </c>
+      <c r="C386">
+        <v>40.7979393005371</v>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>10101</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>Puerto Montt</t>
+        </is>
+      </c>
+      <c r="C387">
+        <v>40.7951583862305</v>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>10204</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>Curaco de Vélez</t>
+        </is>
+      </c>
+      <c r="C388">
+        <v>40.7407417297363</v>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>10208</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>Quellón</t>
+        </is>
+      </c>
+      <c r="C389">
+        <v>40.6163749694824</v>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>10401</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>Chaitén</t>
+        </is>
+      </c>
+      <c r="C390">
+        <v>40.6060600280762</v>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>10304</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>Puyehue</t>
+        </is>
+      </c>
+      <c r="C391">
+        <v>40.5832328796387</v>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>10302</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>Puerto Octay</t>
+        </is>
+      </c>
+      <c r="C392">
+        <v>40.4580154418945</v>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>10307</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>San Pablo</t>
+        </is>
+      </c>
+      <c r="C393">
+        <v>40.3940887451172</v>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>10401</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>Chaitén</t>
+        </is>
+      </c>
+      <c r="C394">
+        <v>40.3614463806152</v>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>10301</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>Osorno</t>
+        </is>
+      </c>
+      <c r="C395">
+        <v>40.2803001403809</v>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>10304</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>Puyehue</t>
+        </is>
+      </c>
+      <c r="C396">
+        <v>40.2383651733398</v>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>10307</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>San Pablo</t>
+        </is>
+      </c>
+      <c r="C397">
+        <v>40.1477813720703</v>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>10101</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>Puerto Montt</t>
+        </is>
+      </c>
+      <c r="C398">
+        <v>40.1385688781738</v>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>10101</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>Puerto Montt</t>
+        </is>
+      </c>
+      <c r="C399">
+        <v>40.0410385131836</v>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>10404</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>Palena</t>
+        </is>
+      </c>
+      <c r="C400">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>10209</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>Quemchi</t>
+        </is>
+      </c>
+      <c r="C401">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>10302</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>Puerto Octay</t>
+        </is>
+      </c>
+      <c r="C402">
+        <v>39.7610931396484</v>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>10302</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>Puerto Octay</t>
+        </is>
+      </c>
+      <c r="C403">
+        <v>39.6566505432129</v>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>10201</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>Castro</t>
+        </is>
+      </c>
+      <c r="C404">
+        <v>39.6499252319336</v>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>10101</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>Puerto Montt</t>
+        </is>
+      </c>
+      <c r="C405">
+        <v>39.6482162475586</v>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>10302</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>Puerto Octay</t>
+        </is>
+      </c>
+      <c r="C406">
+        <v>39.5509490966797</v>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>10404</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>Palena</t>
+        </is>
+      </c>
+      <c r="C407">
+        <v>39.5061721801758</v>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>10307</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>San Pablo</t>
+        </is>
+      </c>
+      <c r="C408">
+        <v>39.4992332458496</v>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>10207</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>Queilén</t>
+        </is>
+      </c>
+      <c r="C409">
+        <v>39.4308929443359</v>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>10109</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>Puerto Varas</t>
+        </is>
+      </c>
+      <c r="C410">
+        <v>39.4196434020996</v>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>10106</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>Los Muermos</t>
+        </is>
+      </c>
+      <c r="C411">
+        <v>39.3827171325684</v>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>10106</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>Los Muermos</t>
+        </is>
+      </c>
+      <c r="C412">
+        <v>39.2592582702637</v>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>10304</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>Puyehue</t>
+        </is>
+      </c>
+      <c r="C413">
+        <v>39.2361106872559</v>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>10305</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>Río Negro</t>
+        </is>
+      </c>
+      <c r="C414">
+        <v>39.0428199768066</v>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>10305</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>Río Negro</t>
+        </is>
+      </c>
+      <c r="C415">
+        <v>38.994800567627</v>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>10301</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>Osorno</t>
+        </is>
+      </c>
+      <c r="C416">
+        <v>38.951488494873</v>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>10404</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>Palena</t>
+        </is>
+      </c>
+      <c r="C417">
+        <v>38.8888893127441</v>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>10402</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>Futaleufú</t>
+        </is>
+      </c>
+      <c r="C418">
+        <v>38.75</v>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>10102</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>Calbuco</t>
+        </is>
+      </c>
+      <c r="C419">
+        <v>38.7283248901367</v>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>10401</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>Chaitén</t>
+        </is>
+      </c>
+      <c r="C420">
+        <v>38.7096786499023</v>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>10208</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>Quellón</t>
+        </is>
+      </c>
+      <c r="C421">
+        <v>38.6462898254395</v>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>10206</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>Puqueldón</t>
+        </is>
+      </c>
+      <c r="C422">
+        <v>38.3458633422851</v>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>10307</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>San Pablo</t>
+        </is>
+      </c>
+      <c r="C423">
+        <v>38.2045936584473</v>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>10303</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>Purranque</t>
+        </is>
+      </c>
+      <c r="C424">
+        <v>38.1726455688477</v>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>10302</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>Puerto Octay</t>
+        </is>
+      </c>
+      <c r="C425">
+        <v>38.1443290710449</v>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>10204</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>Curaco de Vélez</t>
+        </is>
+      </c>
+      <c r="C426">
+        <v>38.016529083252</v>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>10101</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>Puerto Montt</t>
+        </is>
+      </c>
+      <c r="C427">
+        <v>37.957893371582</v>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>10401</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>Chaitén</t>
+        </is>
+      </c>
+      <c r="C428">
+        <v>37.9518089294434</v>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>10104</t>
+        </is>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>Fresia</t>
+        </is>
+      </c>
+      <c r="C429">
+        <v>37.9436340332031</v>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>10104</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>Fresia</t>
+        </is>
+      </c>
+      <c r="C430">
+        <v>37.9421234130859</v>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>10101</t>
+        </is>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>Puerto Montt</t>
+        </is>
+      </c>
+      <c r="C431">
+        <v>37.7563629150391</v>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>10104</t>
+        </is>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>Fresia</t>
+        </is>
+      </c>
+      <c r="C432">
+        <v>37.6906318664551</v>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>10207</t>
+        </is>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>Queilén</t>
+        </is>
+      </c>
+      <c r="C433">
+        <v>37.6854591369629</v>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>10203</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>Chonchi</t>
+        </is>
+      </c>
+      <c r="C434">
+        <v>37.6854591369629</v>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>10304</t>
+        </is>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>Puyehue</t>
+        </is>
+      </c>
+      <c r="C435">
+        <v>37.6670722961426</v>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>10203</t>
+        </is>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>Chonchi</t>
+        </is>
+      </c>
+      <c r="C436">
+        <v>37.5824165344238</v>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>10109</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>Puerto Varas</t>
+        </is>
+      </c>
+      <c r="C437">
+        <v>37.5714302062988</v>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>10109</t>
+        </is>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>Puerto Varas</t>
+        </is>
+      </c>
+      <c r="C438">
+        <v>37.5200004577637</v>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>10109</t>
+        </is>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>Puerto Varas</t>
+        </is>
+      </c>
+      <c r="C439">
+        <v>37.4709968566895</v>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>10208</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>Quellón</t>
+        </is>
+      </c>
+      <c r="C440">
+        <v>37.4301681518555</v>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>10106</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>Los Muermos</t>
+        </is>
+      </c>
+      <c r="C441">
+        <v>37.3004341125488</v>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>10109</t>
+        </is>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>Puerto Varas</t>
+        </is>
+      </c>
+      <c r="C442">
+        <v>37.295825958252</v>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>10403</t>
+        </is>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>Hualaihué</t>
+        </is>
+      </c>
+      <c r="C443">
+        <v>37.2623558044434</v>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>10307</t>
+        </is>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>San Pablo</t>
+        </is>
+      </c>
+      <c r="C444">
+        <v>37.1607513427734</v>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>10106</t>
+        </is>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>Los Muermos</t>
+        </is>
+      </c>
+      <c r="C445">
+        <v>37.1510391235351</v>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>10306</t>
+        </is>
+      </c>
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>San Juan de la Costa</t>
+        </is>
+      </c>
+      <c r="C446">
+        <v>36.9193153381348</v>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>10307</t>
+        </is>
+      </c>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>San Pablo</t>
+        </is>
+      </c>
+      <c r="C447">
+        <v>36.8932037353516</v>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>10304</t>
+        </is>
+      </c>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>Puyehue</t>
+        </is>
+      </c>
+      <c r="C448">
+        <v>36.8674697875977</v>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>10302</t>
+        </is>
+      </c>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>Puerto Octay</t>
+        </is>
+      </c>
+      <c r="C449">
+        <v>36.7875633239746</v>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>10102</t>
+        </is>
+      </c>
+      <c r="B450" t="inlineStr">
+        <is>
+          <t>Calbuco</t>
+        </is>
+      </c>
+      <c r="C450">
+        <v>36.777458190918</v>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>10307</t>
+        </is>
+      </c>
+      <c r="B451" t="inlineStr">
+        <is>
+          <t>San Pablo</t>
+        </is>
+      </c>
+      <c r="C451">
+        <v>36.6377105712891</v>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>10103</t>
+        </is>
+      </c>
+      <c r="B452" t="inlineStr">
+        <is>
+          <t>Cochamó</t>
+        </is>
+      </c>
+      <c r="C452">
+        <v>36.599422454834</v>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>10404</t>
+        </is>
+      </c>
+      <c r="B453" t="inlineStr">
+        <is>
+          <t>Palena</t>
+        </is>
+      </c>
+      <c r="C453">
+        <v>36.3636360168457</v>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>10206</t>
+        </is>
+      </c>
+      <c r="B454" t="inlineStr">
+        <is>
+          <t>Puqueldón</t>
+        </is>
+      </c>
+      <c r="C454">
+        <v>36.3636360168457</v>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>10403</t>
+        </is>
+      </c>
+      <c r="B455" t="inlineStr">
+        <is>
+          <t>Hualaihué</t>
+        </is>
+      </c>
+      <c r="C455">
+        <v>36.32958984375</v>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>10104</t>
+        </is>
+      </c>
+      <c r="B456" t="inlineStr">
+        <is>
+          <t>Fresia</t>
+        </is>
+      </c>
+      <c r="C456">
+        <v>36.2554130554199</v>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>10102</t>
+        </is>
+      </c>
+      <c r="B457" t="inlineStr">
+        <is>
+          <t>Calbuco</t>
+        </is>
+      </c>
+      <c r="C457">
+        <v>36.1513671875</v>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>10209</t>
+        </is>
+      </c>
+      <c r="B458" t="inlineStr">
+        <is>
+          <t>Quemchi</t>
+        </is>
+      </c>
+      <c r="C458">
+        <v>36.1203994750977</v>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>10104</t>
+        </is>
+      </c>
+      <c r="B459" t="inlineStr">
+        <is>
+          <t>Fresia</t>
+        </is>
+      </c>
+      <c r="C459">
+        <v>36.1169090270996</v>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>10103</t>
+        </is>
+      </c>
+      <c r="B460" t="inlineStr">
+        <is>
+          <t>Cochamó</t>
+        </is>
+      </c>
+      <c r="C460">
+        <v>36.0975608825684</v>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>10109</t>
+        </is>
+      </c>
+      <c r="B461" t="inlineStr">
+        <is>
+          <t>Puerto Varas</t>
+        </is>
+      </c>
+      <c r="C461">
+        <v>36.0150375366211</v>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>10104</t>
+        </is>
+      </c>
+      <c r="B462" t="inlineStr">
+        <is>
+          <t>Fresia</t>
+        </is>
+      </c>
+      <c r="C462">
+        <v>35.9879035949707</v>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>10109</t>
+        </is>
+      </c>
+      <c r="B463" t="inlineStr">
+        <is>
+          <t>Puerto Varas</t>
+        </is>
+      </c>
+      <c r="C463">
+        <v>35.9430618286133</v>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>10205</t>
+        </is>
+      </c>
+      <c r="B464" t="inlineStr">
+        <is>
+          <t>Dalcahue</t>
+        </is>
+      </c>
+      <c r="C464">
+        <v>35.9263648986816</v>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>10203</t>
+        </is>
+      </c>
+      <c r="B465" t="inlineStr">
+        <is>
+          <t>Chonchi</t>
+        </is>
+      </c>
+      <c r="C465">
+        <v>35.7601699829102</v>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>10402</t>
+        </is>
+      </c>
+      <c r="B466" t="inlineStr">
+        <is>
+          <t>Futaleufú</t>
+        </is>
+      </c>
+      <c r="C466">
+        <v>35.7142868041992</v>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>10304</t>
+        </is>
+      </c>
+      <c r="B467" t="inlineStr">
+        <is>
+          <t>Puyehue</t>
+        </is>
+      </c>
+      <c r="C467">
+        <v>35.7142868041992</v>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="inlineStr">
+        <is>
+          <t>10304</t>
+        </is>
+      </c>
+      <c r="B468" t="inlineStr">
+        <is>
+          <t>Puyehue</t>
+        </is>
+      </c>
+      <c r="C468">
+        <v>35.7142868041992</v>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>10302</t>
+        </is>
+      </c>
+      <c r="B469" t="inlineStr">
+        <is>
+          <t>Puerto Octay</t>
+        </is>
+      </c>
+      <c r="C469">
+        <v>35.6828193664551</v>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="inlineStr">
+        <is>
+          <t>10402</t>
+        </is>
+      </c>
+      <c r="B470" t="inlineStr">
+        <is>
+          <t>Futaleufú</t>
+        </is>
+      </c>
+      <c r="C470">
+        <v>35.625</v>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="inlineStr">
+        <is>
+          <t>10201</t>
+        </is>
+      </c>
+      <c r="B471" t="inlineStr">
+        <is>
+          <t>Castro</t>
+        </is>
+      </c>
+      <c r="C471">
+        <v>35.4545440673828</v>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="inlineStr">
+        <is>
+          <t>10209</t>
+        </is>
+      </c>
+      <c r="B472" t="inlineStr">
+        <is>
+          <t>Quemchi</t>
+        </is>
+      </c>
+      <c r="C472">
+        <v>35.4471549987793</v>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="inlineStr">
+        <is>
+          <t>10104</t>
+        </is>
+      </c>
+      <c r="B473" t="inlineStr">
+        <is>
+          <t>Fresia</t>
+        </is>
+      </c>
+      <c r="C473">
+        <v>35.3813552856445</v>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="inlineStr">
+        <is>
+          <t>10403</t>
+        </is>
+      </c>
+      <c r="B474" t="inlineStr">
+        <is>
+          <t>Hualaihué</t>
+        </is>
+      </c>
+      <c r="C474">
+        <v>35.2828369140625</v>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="inlineStr">
+        <is>
+          <t>10404</t>
+        </is>
+      </c>
+      <c r="B475" t="inlineStr">
+        <is>
+          <t>Palena</t>
+        </is>
+      </c>
+      <c r="C475">
+        <v>35.2750816345215</v>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="inlineStr">
+        <is>
+          <t>10204</t>
+        </is>
+      </c>
+      <c r="B476" t="inlineStr">
+        <is>
+          <t>Curaco de Vélez</t>
+        </is>
+      </c>
+      <c r="C476">
+        <v>35.0923500061035</v>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="inlineStr">
+        <is>
+          <t>10105</t>
+        </is>
+      </c>
+      <c r="B477" t="inlineStr">
+        <is>
+          <t>Frutillar</t>
+        </is>
+      </c>
+      <c r="C477">
+        <v>35.028247833252</v>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>10402</t>
+        </is>
+      </c>
+      <c r="B478" t="inlineStr">
+        <is>
+          <t>Futaleufú</t>
+        </is>
+      </c>
+      <c r="C478">
+        <v>34.9397583007812</v>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>10202</t>
+        </is>
+      </c>
+      <c r="B479" t="inlineStr">
+        <is>
+          <t>Ancud</t>
+        </is>
+      </c>
+      <c r="C479">
+        <v>34.9056587219238</v>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="inlineStr">
+        <is>
+          <t>10402</t>
+        </is>
+      </c>
+      <c r="B480" t="inlineStr">
+        <is>
+          <t>Futaleufú</t>
+        </is>
+      </c>
+      <c r="C480">
+        <v>34.8189430236816</v>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="inlineStr">
+        <is>
+          <t>10102</t>
+        </is>
+      </c>
+      <c r="B481" t="inlineStr">
+        <is>
+          <t>Calbuco</t>
+        </is>
+      </c>
+      <c r="C481">
+        <v>34.759593963623</v>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="inlineStr">
+        <is>
+          <t>10206</t>
+        </is>
+      </c>
+      <c r="B482" t="inlineStr">
+        <is>
+          <t>Puqueldón</t>
+        </is>
+      </c>
+      <c r="C482">
+        <v>34.6534652709961</v>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="inlineStr">
+        <is>
+          <t>10104</t>
+        </is>
+      </c>
+      <c r="B483" t="inlineStr">
+        <is>
+          <t>Fresia</t>
+        </is>
+      </c>
+      <c r="C483">
+        <v>34.4226570129395</v>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="inlineStr">
+        <is>
+          <t>10208</t>
+        </is>
+      </c>
+      <c r="B484" t="inlineStr">
+        <is>
+          <t>Quellón</t>
+        </is>
+      </c>
+      <c r="C484">
+        <v>34.4199409484863</v>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="inlineStr">
+        <is>
+          <t>10108</t>
+        </is>
+      </c>
+      <c r="B485" t="inlineStr">
+        <is>
+          <t>Maullín</t>
+        </is>
+      </c>
+      <c r="C485">
+        <v>34.4113845825195</v>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="inlineStr">
+        <is>
+          <t>10210</t>
+        </is>
+      </c>
+      <c r="B486" t="inlineStr">
+        <is>
+          <t>Quinchao</t>
+        </is>
+      </c>
+      <c r="C486">
+        <v>34.2379951477051</v>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="inlineStr">
+        <is>
+          <t>10401</t>
+        </is>
+      </c>
+      <c r="B487" t="inlineStr">
+        <is>
+          <t>Chaitén</t>
+        </is>
+      </c>
+      <c r="C487">
+        <v>34.1935501098633</v>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" t="inlineStr">
+        <is>
+          <t>10305</t>
+        </is>
+      </c>
+      <c r="B488" t="inlineStr">
+        <is>
+          <t>Río Negro</t>
+        </is>
+      </c>
+      <c r="C488">
+        <v>34.1421127319336</v>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="inlineStr">
+        <is>
+          <t>10307</t>
+        </is>
+      </c>
+      <c r="B489" t="inlineStr">
+        <is>
+          <t>San Pablo</t>
+        </is>
+      </c>
+      <c r="C489">
+        <v>34.0044746398926</v>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" t="inlineStr">
+        <is>
+          <t>10204</t>
+        </is>
+      </c>
+      <c r="B490" t="inlineStr">
+        <is>
+          <t>Curaco de Vélez</t>
+        </is>
+      </c>
+      <c r="C490">
+        <v>33.9743576049805</v>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" t="inlineStr">
+        <is>
+          <t>10305</t>
+        </is>
+      </c>
+      <c r="B491" t="inlineStr">
+        <is>
+          <t>Río Negro</t>
+        </is>
+      </c>
+      <c r="C491">
+        <v>33.9407730102539</v>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" t="inlineStr">
+        <is>
+          <t>10106</t>
+        </is>
+      </c>
+      <c r="B492" t="inlineStr">
+        <is>
+          <t>Los Muermos</t>
+        </is>
+      </c>
+      <c r="C492">
+        <v>33.8376388549805</v>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" t="inlineStr">
+        <is>
+          <t>10401</t>
+        </is>
+      </c>
+      <c r="B493" t="inlineStr">
+        <is>
+          <t>Chaitén</t>
+        </is>
+      </c>
+      <c r="C493">
+        <v>33.7477798461914</v>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" t="inlineStr">
+        <is>
+          <t>10101</t>
+        </is>
+      </c>
+      <c r="B494" t="inlineStr">
+        <is>
+          <t>Puerto Montt</t>
+        </is>
+      </c>
+      <c r="C494">
+        <v>33.6211051940918</v>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="inlineStr">
+        <is>
+          <t>10306</t>
+        </is>
+      </c>
+      <c r="B495" t="inlineStr">
+        <is>
+          <t>San Juan de la Costa</t>
+        </is>
+      </c>
+      <c r="C495">
+        <v>33.59375</v>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" t="inlineStr">
+        <is>
+          <t>10303</t>
+        </is>
+      </c>
+      <c r="B496" t="inlineStr">
+        <is>
+          <t>Purranque</t>
+        </is>
+      </c>
+      <c r="C496">
+        <v>33.4898262023926</v>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" t="inlineStr">
+        <is>
+          <t>10201</t>
+        </is>
+      </c>
+      <c r="B497" t="inlineStr">
+        <is>
+          <t>Castro</t>
+        </is>
+      </c>
+      <c r="C497">
+        <v>33.463794708252</v>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" t="inlineStr">
+        <is>
+          <t>10403</t>
+        </is>
+      </c>
+      <c r="B498" t="inlineStr">
+        <is>
+          <t>Hualaihué</t>
+        </is>
+      </c>
+      <c r="C498">
+        <v>33.2688598632812</v>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" t="inlineStr">
+        <is>
+          <t>10304</t>
+        </is>
+      </c>
+      <c r="B499" t="inlineStr">
+        <is>
+          <t>Puyehue</t>
+        </is>
+      </c>
+      <c r="C499">
+        <v>33.2530136108398</v>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" t="inlineStr">
+        <is>
+          <t>10107</t>
+        </is>
+      </c>
+      <c r="B500" t="inlineStr">
+        <is>
+          <t>Llanquihue</t>
+        </is>
+      </c>
+      <c r="C500">
+        <v>33.2244911193848</v>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" t="inlineStr">
+        <is>
+          <t>10401</t>
+        </is>
+      </c>
+      <c r="B501" t="inlineStr">
+        <is>
+          <t>Chaitén</t>
+        </is>
+      </c>
+      <c r="C501">
+        <v>33.2015800476074</v>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" t="inlineStr">
+        <is>
+          <t>10403</t>
+        </is>
+      </c>
+      <c r="B502" t="inlineStr">
+        <is>
+          <t>Hualaihué</t>
+        </is>
+      </c>
+      <c r="C502">
+        <v>33.1606216430664</v>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" t="inlineStr">
+        <is>
+          <t>10101</t>
+        </is>
+      </c>
+      <c r="B503" t="inlineStr">
+        <is>
+          <t>Puerto Montt</t>
+        </is>
+      </c>
+      <c r="C503">
+        <v>33.1603660583496</v>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" t="inlineStr">
+        <is>
+          <t>10104</t>
+        </is>
+      </c>
+      <c r="B504" t="inlineStr">
+        <is>
+          <t>Fresia</t>
+        </is>
+      </c>
+      <c r="C504">
+        <v>33.0578498840332</v>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" t="inlineStr">
+        <is>
+          <t>10210</t>
+        </is>
+      </c>
+      <c r="B505" t="inlineStr">
+        <is>
+          <t>Quinchao</t>
+        </is>
+      </c>
+      <c r="C505">
+        <v>33.05322265625</v>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" t="inlineStr">
+        <is>
+          <t>10101</t>
+        </is>
+      </c>
+      <c r="B506" t="inlineStr">
+        <is>
+          <t>Puerto Montt</t>
+        </is>
+      </c>
+      <c r="C506">
+        <v>32.9052619934082</v>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="inlineStr">
+        <is>
+          <t>10102</t>
+        </is>
+      </c>
+      <c r="B507" t="inlineStr">
+        <is>
+          <t>Calbuco</t>
+        </is>
+      </c>
+      <c r="C507">
+        <v>32.8174018859863</v>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="inlineStr">
+        <is>
+          <t>10208</t>
+        </is>
+      </c>
+      <c r="B508" t="inlineStr">
+        <is>
+          <t>Quellón</t>
+        </is>
+      </c>
+      <c r="C508">
+        <v>32.8159637451172</v>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="inlineStr">
+        <is>
+          <t>10202</t>
+        </is>
+      </c>
+      <c r="B509" t="inlineStr">
+        <is>
+          <t>Ancud</t>
+        </is>
+      </c>
+      <c r="C509">
+        <v>32.5921211242676</v>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="inlineStr">
+        <is>
+          <t>10306</t>
+        </is>
+      </c>
+      <c r="B510" t="inlineStr">
+        <is>
+          <t>San Juan de la Costa</t>
+        </is>
+      </c>
+      <c r="C510">
+        <v>32.3270454406738</v>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="inlineStr">
+        <is>
+          <t>10404</t>
+        </is>
+      </c>
+      <c r="B511" t="inlineStr">
+        <is>
+          <t>Palena</t>
+        </is>
+      </c>
+      <c r="C511">
+        <v>32.1428565979004</v>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" t="inlineStr">
+        <is>
+          <t>10103</t>
+        </is>
+      </c>
+      <c r="B512" t="inlineStr">
+        <is>
+          <t>Cochamó</t>
+        </is>
+      </c>
+      <c r="C512">
+        <v>32.0754699707031</v>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="inlineStr">
+        <is>
+          <t>10206</t>
+        </is>
+      </c>
+      <c r="B513" t="inlineStr">
+        <is>
+          <t>Puqueldón</t>
+        </is>
+      </c>
+      <c r="C513">
+        <v>32.0175437927246</v>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="inlineStr">
+        <is>
+          <t>10202</t>
+        </is>
+      </c>
+      <c r="B514" t="inlineStr">
+        <is>
+          <t>Ancud</t>
+        </is>
+      </c>
+      <c r="C514">
+        <v>31.9444446563721</v>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="inlineStr">
+        <is>
+          <t>10103</t>
+        </is>
+      </c>
+      <c r="B515" t="inlineStr">
+        <is>
+          <t>Cochamó</t>
+        </is>
+      </c>
+      <c r="C515">
+        <v>31.8318309783936</v>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="inlineStr">
+        <is>
+          <t>10402</t>
+        </is>
+      </c>
+      <c r="B516" t="inlineStr">
+        <is>
+          <t>Futaleufú</t>
+        </is>
+      </c>
+      <c r="C516">
+        <v>31.6582908630371</v>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="inlineStr">
+        <is>
+          <t>10104</t>
+        </is>
+      </c>
+      <c r="B517" t="inlineStr">
+        <is>
+          <t>Fresia</t>
+        </is>
+      </c>
+      <c r="C517">
+        <v>31.5112533569336</v>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="inlineStr">
+        <is>
+          <t>10302</t>
+        </is>
+      </c>
+      <c r="B518" t="inlineStr">
+        <is>
+          <t>Puerto Octay</t>
+        </is>
+      </c>
+      <c r="C518">
+        <v>31.2977104187012</v>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="inlineStr">
+        <is>
+          <t>10205</t>
+        </is>
+      </c>
+      <c r="B519" t="inlineStr">
+        <is>
+          <t>Dalcahue</t>
+        </is>
+      </c>
+      <c r="C519">
+        <v>31.2169303894043</v>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="inlineStr">
+        <is>
+          <t>10207</t>
+        </is>
+      </c>
+      <c r="B520" t="inlineStr">
+        <is>
+          <t>Queilén</t>
+        </is>
+      </c>
+      <c r="C520">
+        <v>31.1720695495605</v>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="inlineStr">
+        <is>
+          <t>10206</t>
+        </is>
+      </c>
+      <c r="B521" t="inlineStr">
+        <is>
+          <t>Puqueldón</t>
+        </is>
+      </c>
+      <c r="C521">
+        <v>31.1475410461426</v>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="inlineStr">
+        <is>
+          <t>10108</t>
+        </is>
+      </c>
+      <c r="B522" t="inlineStr">
+        <is>
+          <t>Maullín</t>
+        </is>
+      </c>
+      <c r="C522">
+        <v>31.1386528015137</v>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="inlineStr">
+        <is>
+          <t>10102</t>
+        </is>
+      </c>
+      <c r="B523" t="inlineStr">
+        <is>
+          <t>Calbuco</t>
+        </is>
+      </c>
+      <c r="C523">
+        <v>31.0660305023193</v>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" t="inlineStr">
+        <is>
+          <t>10205</t>
+        </is>
+      </c>
+      <c r="B524" t="inlineStr">
+        <is>
+          <t>Dalcahue</t>
+        </is>
+      </c>
+      <c r="C524">
+        <v>30.8668079376221</v>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="inlineStr">
+        <is>
+          <t>10302</t>
+        </is>
+      </c>
+      <c r="B525" t="inlineStr">
+        <is>
+          <t>Puerto Octay</t>
+        </is>
+      </c>
+      <c r="C525">
+        <v>30.8370037078857</v>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" t="inlineStr">
+        <is>
+          <t>10303</t>
+        </is>
+      </c>
+      <c r="B526" t="inlineStr">
+        <is>
+          <t>Purranque</t>
+        </is>
+      </c>
+      <c r="C526">
+        <v>30.7598037719727</v>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="inlineStr">
+        <is>
+          <t>10103</t>
+        </is>
+      </c>
+      <c r="B527" t="inlineStr">
+        <is>
+          <t>Cochamó</t>
+        </is>
+      </c>
+      <c r="C527">
+        <v>30.701753616333</v>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="inlineStr">
+        <is>
+          <t>10204</t>
+        </is>
+      </c>
+      <c r="B528" t="inlineStr">
+        <is>
+          <t>Curaco de Vélez</t>
+        </is>
+      </c>
+      <c r="C528">
+        <v>30.6451606750488</v>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="inlineStr">
+        <is>
+          <t>10404</t>
+        </is>
+      </c>
+      <c r="B529" t="inlineStr">
+        <is>
+          <t>Palena</t>
+        </is>
+      </c>
+      <c r="C529">
+        <v>30.6122455596924</v>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" t="inlineStr">
+        <is>
+          <t>10207</t>
+        </is>
+      </c>
+      <c r="B530" t="inlineStr">
+        <is>
+          <t>Queilén</t>
+        </is>
+      </c>
+      <c r="C530">
+        <v>30.5936069488525</v>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" t="inlineStr">
+        <is>
+          <t>10106</t>
+        </is>
+      </c>
+      <c r="B531" t="inlineStr">
+        <is>
+          <t>Los Muermos</t>
+        </is>
+      </c>
+      <c r="C531">
+        <v>30.3122615814209</v>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" t="inlineStr">
+        <is>
+          <t>10201</t>
+        </is>
+      </c>
+      <c r="B532" t="inlineStr">
+        <is>
+          <t>Castro</t>
+        </is>
+      </c>
+      <c r="C532">
+        <v>30.142993927002</v>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" t="inlineStr">
+        <is>
+          <t>10204</t>
+        </is>
+      </c>
+      <c r="B533" t="inlineStr">
+        <is>
+          <t>Curaco de Vélez</t>
+        </is>
+      </c>
+      <c r="C533">
+        <v>29.9212589263916</v>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" t="inlineStr">
+        <is>
+          <t>10108</t>
+        </is>
+      </c>
+      <c r="B534" t="inlineStr">
+        <is>
+          <t>Maullín</t>
+        </is>
+      </c>
+      <c r="C534">
+        <v>29.9065418243408</v>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" t="inlineStr">
+        <is>
+          <t>10402</t>
+        </is>
+      </c>
+      <c r="B535" t="inlineStr">
+        <is>
+          <t>Futaleufú</t>
+        </is>
+      </c>
+      <c r="C535">
+        <v>29.5918369293213</v>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" t="inlineStr">
+        <is>
+          <t>10301</t>
+        </is>
+      </c>
+      <c r="B536" t="inlineStr">
+        <is>
+          <t>Osorno</t>
+        </is>
+      </c>
+      <c r="C536">
+        <v>29.5469417572021</v>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" t="inlineStr">
+        <is>
+          <t>10210</t>
+        </is>
+      </c>
+      <c r="B537" t="inlineStr">
+        <is>
+          <t>Quinchao</t>
+        </is>
+      </c>
+      <c r="C537">
+        <v>29.5031051635742</v>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" t="inlineStr">
+        <is>
+          <t>10108</t>
+        </is>
+      </c>
+      <c r="B538" t="inlineStr">
+        <is>
+          <t>Maullín</t>
+        </is>
+      </c>
+      <c r="C538">
+        <v>29.474515914917</v>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" t="inlineStr">
+        <is>
+          <t>10209</t>
+        </is>
+      </c>
+      <c r="B539" t="inlineStr">
+        <is>
+          <t>Quemchi</t>
+        </is>
+      </c>
+      <c r="C539">
+        <v>29.4336814880371</v>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" t="inlineStr">
+        <is>
+          <t>10305</t>
+        </is>
+      </c>
+      <c r="B540" t="inlineStr">
+        <is>
+          <t>Río Negro</t>
+        </is>
+      </c>
+      <c r="C540">
+        <v>29.3924465179443</v>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" t="inlineStr">
+        <is>
+          <t>10305</t>
+        </is>
+      </c>
+      <c r="B541" t="inlineStr">
+        <is>
+          <t>Río Negro</t>
+        </is>
+      </c>
+      <c r="C541">
+        <v>29.1423816680908</v>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" t="inlineStr">
+        <is>
+          <t>10403</t>
+        </is>
+      </c>
+      <c r="B542" t="inlineStr">
+        <is>
+          <t>Hualaihué</t>
+        </is>
+      </c>
+      <c r="C542">
+        <v>29.0801181793213</v>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="inlineStr">
+        <is>
+          <t>10303</t>
+        </is>
+      </c>
+      <c r="B543" t="inlineStr">
+        <is>
+          <t>Purranque</t>
+        </is>
+      </c>
+      <c r="C543">
+        <v>29.0726051330566</v>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" t="inlineStr">
+        <is>
+          <t>10203</t>
+        </is>
+      </c>
+      <c r="B544" t="inlineStr">
+        <is>
+          <t>Chonchi</t>
+        </is>
+      </c>
+      <c r="C544">
+        <v>28.8633460998535</v>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" t="inlineStr">
+        <is>
+          <t>10207</t>
+        </is>
+      </c>
+      <c r="B545" t="inlineStr">
+        <is>
+          <t>Queilén</t>
+        </is>
+      </c>
+      <c r="C545">
+        <v>28.8590602874756</v>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" t="inlineStr">
+        <is>
+          <t>10401</t>
+        </is>
+      </c>
+      <c r="B546" t="inlineStr">
+        <is>
+          <t>Chaitén</t>
+        </is>
+      </c>
+      <c r="C546">
+        <v>28.5714282989502</v>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" t="inlineStr">
+        <is>
+          <t>10106</t>
+        </is>
+      </c>
+      <c r="B547" t="inlineStr">
+        <is>
+          <t>Los Muermos</t>
+        </is>
+      </c>
+      <c r="C547">
+        <v>28.35595703125</v>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" t="inlineStr">
+        <is>
+          <t>10102</t>
+        </is>
+      </c>
+      <c r="B548" t="inlineStr">
+        <is>
+          <t>Calbuco</t>
+        </is>
+      </c>
+      <c r="C548">
+        <v>28.2222213745117</v>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" t="inlineStr">
+        <is>
+          <t>10104</t>
+        </is>
+      </c>
+      <c r="B549" t="inlineStr">
+        <is>
+          <t>Fresia</t>
+        </is>
+      </c>
+      <c r="C549">
+        <v>28.1385288238525</v>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" t="inlineStr">
+        <is>
+          <t>10201</t>
+        </is>
+      </c>
+      <c r="B550" t="inlineStr">
+        <is>
+          <t>Castro</t>
+        </is>
+      </c>
+      <c r="C550">
+        <v>28.110237121582</v>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" t="inlineStr">
+        <is>
+          <t>10210</t>
+        </is>
+      </c>
+      <c r="B551" t="inlineStr">
+        <is>
+          <t>Quinchao</t>
+        </is>
+      </c>
+      <c r="C551">
+        <v>28.105094909668</v>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" t="inlineStr">
+        <is>
+          <t>10306</t>
+        </is>
+      </c>
+      <c r="B552" t="inlineStr">
+        <is>
+          <t>San Juan de la Costa</t>
+        </is>
+      </c>
+      <c r="C552">
         <v>27.8541946411133</v>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" t="inlineStr">
+        <is>
+          <t>10304</t>
+        </is>
+      </c>
+      <c r="B553" t="inlineStr">
+        <is>
+          <t>Puyehue</t>
+        </is>
+      </c>
+      <c r="C553">
+        <v>27.8093070983887</v>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" t="inlineStr">
+        <is>
+          <t>10202</t>
+        </is>
+      </c>
+      <c r="B554" t="inlineStr">
+        <is>
+          <t>Ancud</t>
+        </is>
+      </c>
+      <c r="C554">
+        <v>27.7863636016846</v>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" t="inlineStr">
+        <is>
+          <t>10108</t>
+        </is>
+      </c>
+      <c r="B555" t="inlineStr">
+        <is>
+          <t>Maullín</t>
+        </is>
+      </c>
+      <c r="C555">
+        <v>27.7419357299805</v>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" t="inlineStr">
+        <is>
+          <t>10303</t>
+        </is>
+      </c>
+      <c r="B556" t="inlineStr">
+        <is>
+          <t>Purranque</t>
+        </is>
+      </c>
+      <c r="C556">
+        <v>27.6978416442871</v>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" t="inlineStr">
+        <is>
+          <t>10301</t>
+        </is>
+      </c>
+      <c r="B557" t="inlineStr">
+        <is>
+          <t>Osorno</t>
+        </is>
+      </c>
+      <c r="C557">
+        <v>27.3812618255615</v>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" t="inlineStr">
+        <is>
+          <t>10302</t>
+        </is>
+      </c>
+      <c r="B558" t="inlineStr">
+        <is>
+          <t>Puerto Octay</t>
+        </is>
+      </c>
+      <c r="C558">
+        <v>27.2103004455566</v>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" t="inlineStr">
+        <is>
+          <t>10101</t>
+        </is>
+      </c>
+      <c r="B559" t="inlineStr">
+        <is>
+          <t>Puerto Montt</t>
+        </is>
+      </c>
+      <c r="C559">
+        <v>27.097240447998</v>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" t="inlineStr">
+        <is>
+          <t>10109</t>
+        </is>
+      </c>
+      <c r="B560" t="inlineStr">
+        <is>
+          <t>Puerto Varas</t>
+        </is>
+      </c>
+      <c r="C560">
+        <v>27.0676689147949</v>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" t="inlineStr">
+        <is>
+          <t>10307</t>
+        </is>
+      </c>
+      <c r="B561" t="inlineStr">
+        <is>
+          <t>San Pablo</t>
+        </is>
+      </c>
+      <c r="C561">
+        <v>26.8799991607666</v>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" t="inlineStr">
+        <is>
+          <t>10101</t>
+        </is>
+      </c>
+      <c r="B562" t="inlineStr">
+        <is>
+          <t>Puerto Montt</t>
+        </is>
+      </c>
+      <c r="C562">
+        <v>26.7575054168701</v>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" t="inlineStr">
+        <is>
+          <t>10103</t>
+        </is>
+      </c>
+      <c r="B563" t="inlineStr">
+        <is>
+          <t>Cochamó</t>
+        </is>
+      </c>
+      <c r="C563">
+        <v>26.6457672119141</v>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" t="inlineStr">
+        <is>
+          <t>10105</t>
+        </is>
+      </c>
+      <c r="B564" t="inlineStr">
+        <is>
+          <t>Frutillar</t>
+        </is>
+      </c>
+      <c r="C564">
+        <v>26.2435684204102</v>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" t="inlineStr">
+        <is>
+          <t>10203</t>
+        </is>
+      </c>
+      <c r="B565" t="inlineStr">
+        <is>
+          <t>Chonchi</t>
+        </is>
+      </c>
+      <c r="C565">
+        <v>26.2385330200195</v>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" t="inlineStr">
+        <is>
+          <t>10302</t>
+        </is>
+      </c>
+      <c r="B566" t="inlineStr">
+        <is>
+          <t>Puerto Octay</t>
+        </is>
+      </c>
+      <c r="C566">
+        <v>26.0416660308838</v>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" t="inlineStr">
+        <is>
+          <t>10202</t>
+        </is>
+      </c>
+      <c r="B567" t="inlineStr">
+        <is>
+          <t>Ancud</t>
+        </is>
+      </c>
+      <c r="C567">
+        <v>25.9040107727051</v>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" t="inlineStr">
+        <is>
+          <t>10307</t>
+        </is>
+      </c>
+      <c r="B568" t="inlineStr">
+        <is>
+          <t>San Pablo</t>
+        </is>
+      </c>
+      <c r="C568">
+        <v>25.8252429962158</v>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" t="inlineStr">
+        <is>
+          <t>10109</t>
+        </is>
+      </c>
+      <c r="B569" t="inlineStr">
+        <is>
+          <t>Puerto Varas</t>
+        </is>
+      </c>
+      <c r="C569">
+        <v>25.6805801391602</v>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" t="inlineStr">
+        <is>
+          <t>10106</t>
+        </is>
+      </c>
+      <c r="B570" t="inlineStr">
+        <is>
+          <t>Los Muermos</t>
+        </is>
+      </c>
+      <c r="C570">
+        <v>25.5474452972412</v>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" t="inlineStr">
+        <is>
+          <t>10109</t>
+        </is>
+      </c>
+      <c r="B571" t="inlineStr">
+        <is>
+          <t>Puerto Varas</t>
+        </is>
+      </c>
+      <c r="C571">
+        <v>25.5220413208008</v>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" t="inlineStr">
+        <is>
+          <t>10107</t>
+        </is>
+      </c>
+      <c r="B572" t="inlineStr">
+        <is>
+          <t>Llanquihue</t>
+        </is>
+      </c>
+      <c r="C572">
+        <v>25.4799308776855</v>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" t="inlineStr">
+        <is>
+          <t>10402</t>
+        </is>
+      </c>
+      <c r="B573" t="inlineStr">
+        <is>
+          <t>Futaleufú</t>
+        </is>
+      </c>
+      <c r="C573">
+        <v>25.3012046813965</v>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" t="inlineStr">
+        <is>
+          <t>10208</t>
+        </is>
+      </c>
+      <c r="B574" t="inlineStr">
+        <is>
+          <t>Quellón</t>
+        </is>
+      </c>
+      <c r="C574">
+        <v>25.2747249603271</v>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" t="inlineStr">
+        <is>
+          <t>10105</t>
+        </is>
+      </c>
+      <c r="B575" t="inlineStr">
+        <is>
+          <t>Frutillar</t>
+        </is>
+      </c>
+      <c r="C575">
+        <v>25.174825668335</v>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" t="inlineStr">
+        <is>
+          <t>10205</t>
+        </is>
+      </c>
+      <c r="B576" t="inlineStr">
+        <is>
+          <t>Dalcahue</t>
+        </is>
+      </c>
+      <c r="C576">
+        <v>24.9480247497559</v>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" t="inlineStr">
+        <is>
+          <t>10304</t>
+        </is>
+      </c>
+      <c r="B577" t="inlineStr">
+        <is>
+          <t>Puyehue</t>
+        </is>
+      </c>
+      <c r="C577">
+        <v>24.9443206787109</v>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" t="inlineStr">
+        <is>
+          <t>10108</t>
+        </is>
+      </c>
+      <c r="B578" t="inlineStr">
+        <is>
+          <t>Maullín</t>
+        </is>
+      </c>
+      <c r="C578">
+        <v>24.7933883666992</v>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" t="inlineStr">
+        <is>
+          <t>10303</t>
+        </is>
+      </c>
+      <c r="B579" t="inlineStr">
+        <is>
+          <t>Purranque</t>
+        </is>
+      </c>
+      <c r="C579">
+        <v>24.772497177124</v>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" t="inlineStr">
+        <is>
+          <t>10206</t>
+        </is>
+      </c>
+      <c r="B580" t="inlineStr">
+        <is>
+          <t>Puqueldón</t>
+        </is>
+      </c>
+      <c r="C580">
+        <v>24.615385055542</v>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" t="inlineStr">
+        <is>
+          <t>10205</t>
+        </is>
+      </c>
+      <c r="B581" t="inlineStr">
+        <is>
+          <t>Dalcahue</t>
+        </is>
+      </c>
+      <c r="C581">
+        <v>24.6006393432617</v>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" t="inlineStr">
+        <is>
+          <t>10207</t>
+        </is>
+      </c>
+      <c r="B582" t="inlineStr">
+        <is>
+          <t>Queilén</t>
+        </is>
+      </c>
+      <c r="C582">
+        <v>24.5989303588867</v>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" t="inlineStr">
+        <is>
+          <t>10209</t>
+        </is>
+      </c>
+      <c r="B583" t="inlineStr">
+        <is>
+          <t>Quemchi</t>
+        </is>
+      </c>
+      <c r="C583">
+        <v>24.3466300964355</v>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" t="inlineStr">
+        <is>
+          <t>10210</t>
+        </is>
+      </c>
+      <c r="B584" t="inlineStr">
+        <is>
+          <t>Quinchao</t>
+        </is>
+      </c>
+      <c r="C584">
+        <v>24.3243236541748</v>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" t="inlineStr">
+        <is>
+          <t>10301</t>
+        </is>
+      </c>
+      <c r="B585" t="inlineStr">
+        <is>
+          <t>Osorno</t>
+        </is>
+      </c>
+      <c r="C585">
+        <v>24.1460075378418</v>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" t="inlineStr">
+        <is>
+          <t>10105</t>
+        </is>
+      </c>
+      <c r="B586" t="inlineStr">
+        <is>
+          <t>Frutillar</t>
+        </is>
+      </c>
+      <c r="C586">
+        <v>24.1364421844482</v>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" t="inlineStr">
+        <is>
+          <t>10102</t>
+        </is>
+      </c>
+      <c r="B587" t="inlineStr">
+        <is>
+          <t>Calbuco</t>
+        </is>
+      </c>
+      <c r="C587">
+        <v>24.0637454986572</v>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" t="inlineStr">
+        <is>
+          <t>10108</t>
+        </is>
+      </c>
+      <c r="B588" t="inlineStr">
+        <is>
+          <t>Maullín</t>
+        </is>
+      </c>
+      <c r="C588">
+        <v>23.6790599822998</v>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" t="inlineStr">
+        <is>
+          <t>10301</t>
+        </is>
+      </c>
+      <c r="B589" t="inlineStr">
+        <is>
+          <t>Osorno</t>
+        </is>
+      </c>
+      <c r="C589">
+        <v>23.639554977417</v>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" t="inlineStr">
+        <is>
+          <t>10401</t>
+        </is>
+      </c>
+      <c r="B590" t="inlineStr">
+        <is>
+          <t>Chaitén</t>
+        </is>
+      </c>
+      <c r="C590">
+        <v>23.6363639831543</v>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" t="inlineStr">
+        <is>
+          <t>10210</t>
+        </is>
+      </c>
+      <c r="B591" t="inlineStr">
+        <is>
+          <t>Quinchao</t>
+        </is>
+      </c>
+      <c r="C591">
+        <v>23.5741443634033</v>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" t="inlineStr">
+        <is>
+          <t>10105</t>
+        </is>
+      </c>
+      <c r="B592" t="inlineStr">
+        <is>
+          <t>Frutillar</t>
+        </is>
+      </c>
+      <c r="C592">
+        <v>23.5521240234375</v>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" t="inlineStr">
+        <is>
+          <t>10206</t>
+        </is>
+      </c>
+      <c r="B593" t="inlineStr">
+        <is>
+          <t>Puqueldón</t>
+        </is>
+      </c>
+      <c r="C593">
+        <v>23.4449768066406</v>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" t="inlineStr">
+        <is>
+          <t>10210</t>
+        </is>
+      </c>
+      <c r="B594" t="inlineStr">
+        <is>
+          <t>Quinchao</t>
+        </is>
+      </c>
+      <c r="C594">
+        <v>23.2484073638916</v>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" t="inlineStr">
+        <is>
+          <t>10301</t>
+        </is>
+      </c>
+      <c r="B595" t="inlineStr">
+        <is>
+          <t>Osorno</t>
+        </is>
+      </c>
+      <c r="C595">
+        <v>22.7541103363037</v>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" t="inlineStr">
+        <is>
+          <t>10201</t>
+        </is>
+      </c>
+      <c r="B596" t="inlineStr">
+        <is>
+          <t>Castro</t>
+        </is>
+      </c>
+      <c r="C596">
+        <v>22.5866050720215</v>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" t="inlineStr">
+        <is>
+          <t>10402</t>
+        </is>
+      </c>
+      <c r="B597" t="inlineStr">
+        <is>
+          <t>Futaleufú</t>
+        </is>
+      </c>
+      <c r="C597">
+        <v>22.5</v>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" t="inlineStr">
+        <is>
+          <t>10306</t>
+        </is>
+      </c>
+      <c r="B598" t="inlineStr">
+        <is>
+          <t>San Juan de la Costa</t>
+        </is>
+      </c>
+      <c r="C598">
+        <v>22.4582710266113</v>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" t="inlineStr">
+        <is>
+          <t>10107</t>
+        </is>
+      </c>
+      <c r="B599" t="inlineStr">
+        <is>
+          <t>Llanquihue</t>
+        </is>
+      </c>
+      <c r="C599">
+        <v>22.4444446563721</v>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" t="inlineStr">
+        <is>
+          <t>10202</t>
+        </is>
+      </c>
+      <c r="B600" t="inlineStr">
+        <is>
+          <t>Ancud</t>
+        </is>
+      </c>
+      <c r="C600">
+        <v>22.1308403015137</v>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" t="inlineStr">
+        <is>
+          <t>10302</t>
+        </is>
+      </c>
+      <c r="B601" t="inlineStr">
+        <is>
+          <t>Puerto Octay</t>
+        </is>
+      </c>
+      <c r="C601">
+        <v>21.6494846343994</v>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" t="inlineStr">
+        <is>
+          <t>10305</t>
+        </is>
+      </c>
+      <c r="B602" t="inlineStr">
+        <is>
+          <t>Río Negro</t>
+        </is>
+      </c>
+      <c r="C602">
+        <v>21.6216220855713</v>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" t="inlineStr">
+        <is>
+          <t>10107</t>
+        </is>
+      </c>
+      <c r="B603" t="inlineStr">
+        <is>
+          <t>Llanquihue</t>
+        </is>
+      </c>
+      <c r="C603">
+        <v>21.5296192169189</v>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" t="inlineStr">
+        <is>
+          <t>10209</t>
+        </is>
+      </c>
+      <c r="B604" t="inlineStr">
+        <is>
+          <t>Quemchi</t>
+        </is>
+      </c>
+      <c r="C604">
+        <v>21.2230224609375</v>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" t="inlineStr">
+        <is>
+          <t>10304</t>
+        </is>
+      </c>
+      <c r="B605" t="inlineStr">
+        <is>
+          <t>Puyehue</t>
+        </is>
+      </c>
+      <c r="C605">
+        <v>20.8333339691162</v>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" t="inlineStr">
+        <is>
+          <t>10306</t>
+        </is>
+      </c>
+      <c r="B606" t="inlineStr">
+        <is>
+          <t>San Juan de la Costa</t>
+        </is>
+      </c>
+      <c r="C606">
+        <v>20.8029193878174</v>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" t="inlineStr">
+        <is>
+          <t>10403</t>
+        </is>
+      </c>
+      <c r="B607" t="inlineStr">
+        <is>
+          <t>Hualaihué</t>
+        </is>
+      </c>
+      <c r="C607">
+        <v>20.7317066192627</v>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" t="inlineStr">
+        <is>
+          <t>10105</t>
+        </is>
+      </c>
+      <c r="B608" t="inlineStr">
+        <is>
+          <t>Frutillar</t>
+        </is>
+      </c>
+      <c r="C608">
+        <v>20.4834613800049</v>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" t="inlineStr">
+        <is>
+          <t>10201</t>
+        </is>
+      </c>
+      <c r="B609" t="inlineStr">
+        <is>
+          <t>Castro</t>
+        </is>
+      </c>
+      <c r="C609">
+        <v>20.256254196167</v>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" t="inlineStr">
+        <is>
+          <t>10202</t>
+        </is>
+      </c>
+      <c r="B610" t="inlineStr">
+        <is>
+          <t>Ancud</t>
+        </is>
+      </c>
+      <c r="C610">
+        <v>20.0226249694824</v>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" t="inlineStr">
+        <is>
+          <t>10109</t>
+        </is>
+      </c>
+      <c r="B611" t="inlineStr">
+        <is>
+          <t>Puerto Varas</t>
+        </is>
+      </c>
+      <c r="C611">
+        <v>19.7551021575928</v>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" t="inlineStr">
+        <is>
+          <t>10107</t>
+        </is>
+      </c>
+      <c r="B612" t="inlineStr">
+        <is>
+          <t>Llanquihue</t>
+        </is>
+      </c>
+      <c r="C612">
+        <v>19.5378150939941</v>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" t="inlineStr">
+        <is>
+          <t>10401</t>
+        </is>
+      </c>
+      <c r="B613" t="inlineStr">
+        <is>
+          <t>Chaitén</t>
+        </is>
+      </c>
+      <c r="C613">
+        <v>19.4690265655518</v>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" t="inlineStr">
+        <is>
+          <t>10305</t>
+        </is>
+      </c>
+      <c r="B614" t="inlineStr">
+        <is>
+          <t>Río Negro</t>
+        </is>
+      </c>
+      <c r="C614">
+        <v>19.4054508209229</v>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" t="inlineStr">
+        <is>
+          <t>10103</t>
+        </is>
+      </c>
+      <c r="B615" t="inlineStr">
+        <is>
+          <t>Cochamó</t>
+        </is>
+      </c>
+      <c r="C615">
+        <v>19.1489353179932</v>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" t="inlineStr">
+        <is>
+          <t>10109</t>
+        </is>
+      </c>
+      <c r="B616" t="inlineStr">
+        <is>
+          <t>Puerto Varas</t>
+        </is>
+      </c>
+      <c r="C616">
+        <v>19.1200008392334</v>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" t="inlineStr">
+        <is>
+          <t>10107</t>
+        </is>
+      </c>
+      <c r="B617" t="inlineStr">
+        <is>
+          <t>Llanquihue</t>
+        </is>
+      </c>
+      <c r="C617">
+        <v>18.4796848297119</v>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" t="inlineStr">
+        <is>
+          <t>10303</t>
+        </is>
+      </c>
+      <c r="B618" t="inlineStr">
+        <is>
+          <t>Purranque</t>
+        </is>
+      </c>
+      <c r="C618">
+        <v>18.2061576843262</v>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" t="inlineStr">
+        <is>
+          <t>10209</t>
+        </is>
+      </c>
+      <c r="B619" t="inlineStr">
+        <is>
+          <t>Quemchi</t>
+        </is>
+      </c>
+      <c r="C619">
+        <v>17.9220771789551</v>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" t="inlineStr">
+        <is>
+          <t>10302</t>
+        </is>
+      </c>
+      <c r="B620" t="inlineStr">
+        <is>
+          <t>Puerto Octay</t>
+        </is>
+      </c>
+      <c r="C620">
+        <v>17.7474403381348</v>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" t="inlineStr">
+        <is>
+          <t>10101</t>
+        </is>
+      </c>
+      <c r="B621" t="inlineStr">
+        <is>
+          <t>Puerto Montt</t>
+        </is>
+      </c>
+      <c r="C621">
+        <v>17.7291374206543</v>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" t="inlineStr">
+        <is>
+          <t>10101</t>
+        </is>
+      </c>
+      <c r="B622" t="inlineStr">
+        <is>
+          <t>Puerto Montt</t>
+        </is>
+      </c>
+      <c r="C622">
+        <v>17.5669841766357</v>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" t="inlineStr">
+        <is>
+          <t>10301</t>
+        </is>
+      </c>
+      <c r="B623" t="inlineStr">
+        <is>
+          <t>Osorno</t>
+        </is>
+      </c>
+      <c r="C623">
+        <v>16.948356628418</v>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" t="inlineStr">
+        <is>
+          <t>10304</t>
+        </is>
+      </c>
+      <c r="B624" t="inlineStr">
+        <is>
+          <t>Puyehue</t>
+        </is>
+      </c>
+      <c r="C624">
+        <v>16.6134185791016</v>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" t="inlineStr">
+        <is>
+          <t>10306</t>
+        </is>
+      </c>
+      <c r="B625" t="inlineStr">
+        <is>
+          <t>San Juan de la Costa</t>
+        </is>
+      </c>
+      <c r="C625">
+        <v>16.537467956543</v>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" t="inlineStr">
+        <is>
+          <t>10404</t>
+        </is>
+      </c>
+      <c r="B626" t="inlineStr">
+        <is>
+          <t>Palena</t>
+        </is>
+      </c>
+      <c r="C626">
+        <v>15.3061227798462</v>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" t="inlineStr">
+        <is>
+          <t>10301</t>
+        </is>
+      </c>
+      <c r="B627" t="inlineStr">
+        <is>
+          <t>Osorno</t>
+        </is>
+      </c>
+      <c r="C627">
+        <v>12.704174041748</v>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" t="inlineStr">
+        <is>
+          <t>10109</t>
+        </is>
+      </c>
+      <c r="B628" t="inlineStr">
+        <is>
+          <t>Puerto Varas</t>
+        </is>
+      </c>
+      <c r="C628">
+        <v>12.2775802612305</v>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" t="inlineStr">
+        <is>
+          <t>10105</t>
+        </is>
+      </c>
+      <c r="B629" t="inlineStr">
+        <is>
+          <t>Frutillar</t>
+        </is>
+      </c>
+      <c r="C629">
+        <v>11.6063137054443</v>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" t="inlineStr">
+        <is>
+          <t>10109</t>
+        </is>
+      </c>
+      <c r="B630" t="inlineStr">
+        <is>
+          <t>Puerto Varas</t>
+        </is>
+      </c>
+      <c r="C630">
+        <v>11.0714282989502</v>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" t="inlineStr">
+        <is>
+          <t>10107</t>
+        </is>
+      </c>
+      <c r="B631" t="inlineStr">
+        <is>
+          <t>Llanquihue</t>
+        </is>
+      </c>
+      <c r="C631">
+        <v>7.71456146240234</v>
       </c>
     </row>
   </sheetData>
